--- a/detectors/sketch/dataset/dataset.xlsx
+++ b/detectors/sketch/dataset/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nl2sql\detectors\sketch\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08ABB6C1-CC57-4E9D-B028-A9721C401423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF20E3A-52F5-4A50-9285-057762FC0418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="423">
   <si>
     <t>No</t>
   </si>
@@ -44,1230 +44,21 @@
     <t>SELECT * FROM $TABLE</t>
   </si>
   <si>
-    <t>tampilkan semua data mahasiswa</t>
-  </si>
-  <si>
-    <t>ambil seluruh informasi dari tabel dosen</t>
-  </si>
-  <si>
-    <t>lihat semua mata_kuliah yang tersedia</t>
-  </si>
-  <si>
-    <t>tampilkan daftar kelas lengkap</t>
-  </si>
-  <si>
-    <t>ambil seluruh jadwal perkuliahan</t>
-  </si>
-  <si>
-    <t>tampilkan semua pendaftaran_kelas mahasiswa</t>
-  </si>
-  <si>
-    <t>lihat seluruh nilai yang tercatat</t>
-  </si>
-  <si>
-    <t>ambil semua data dari tabel mahasiswa</t>
-  </si>
-  <si>
-    <t>tampilkan seluruh informasi dosen pengajar</t>
-  </si>
-  <si>
-    <t>lihat daftar semua mata_kuliah yang terdaftar</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari tabel akun</t>
-  </si>
-  <si>
-    <t>ambil semua informasi dari akun</t>
-  </si>
-  <si>
-    <t>perlihatkan seluruh isi tabel jurnal</t>
-  </si>
-  <si>
-    <t>lihat semua data pada tabel detail_jurnal</t>
-  </si>
-  <si>
-    <t>tampilkan semua kolom dari tabel pengguna</t>
-  </si>
-  <si>
-    <t>ambil data lengkap dari tabel buku_besar</t>
-  </si>
-  <si>
-    <t>berikan semua baris dari tabel akun</t>
-  </si>
-  <si>
-    <t>tampilkan seluruh record pada tabel jurnal</t>
-  </si>
-  <si>
-    <t>tampilkan semua entri dalam tabel pengguna</t>
-  </si>
-  <si>
-    <t>perlihatkan data lengkap dari buku_besar</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>ambil seluruh isi tabel kamar</t>
-  </si>
-  <si>
-    <t>perlihatkan semua reservasi yang ada</t>
-  </si>
-  <si>
-    <t>dapatkan data lengkap dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>tampilkan seluruh data staf hotel</t>
-  </si>
-  <si>
-    <t>ambil semua informasi dari jeniskamar</t>
-  </si>
-  <si>
-    <t>tampilkan seluruh record dari tabel reservasi</t>
-  </si>
-  <si>
-    <t>perlihatkan data lengkap semua kamar</t>
-  </si>
-  <si>
-    <t>ambil semua data pelanggan yang tersimpan</t>
-  </si>
-  <si>
-    <t>tampilkan seluruh informasi pembayaran</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari produk</t>
-  </si>
-  <si>
-    <t>ambil seluruh isi tabel kategori</t>
-  </si>
-  <si>
-    <t>lihat data lengkap dari pesananpembelian</t>
-  </si>
-  <si>
-    <t>tampilkan semua baris pada tabel pelanggan</t>
-  </si>
-  <si>
-    <t>ambil semua data dari detailpesananpenjualan</t>
-  </si>
-  <si>
-    <t>tampilkan isi lengkap tabel pemasok</t>
-  </si>
-  <si>
-    <t>lihat semua data yang ada di detailpesananpembelian</t>
-  </si>
-  <si>
-    <t>ambil seluruh informasi dari tabel pesananpenjualan</t>
-  </si>
-  <si>
-    <t>tampilkan semua record dari tabel produk</t>
-  </si>
-  <si>
-    <t>lihat data lengkap yang ada di tabel kategori</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari pegawai</t>
-  </si>
-  <si>
-    <t>ambil seluruh informasi dari jabatan</t>
-  </si>
-  <si>
-    <t>lihat semua entri di divisi</t>
-  </si>
-  <si>
-    <t>tampilkan semua absensi yang tercatat</t>
-  </si>
-  <si>
-    <t>ambil seluruh data gaji karyawan</t>
-  </si>
-  <si>
-    <t>tampilkan data lengkap pegawai</t>
-  </si>
-  <si>
-    <t>lihat seluruh daftar jabatan yang ada</t>
-  </si>
-  <si>
-    <t>ambil semua data divisi di perusahaan</t>
-  </si>
-  <si>
-    <t>tampilkan semua record absensi</t>
-  </si>
-  <si>
-    <t>lihat seluruh data gaji bulanan</t>
-  </si>
-  <si>
-    <t>tampilkan semua data pelanggan</t>
-  </si>
-  <si>
-    <t>ambil seluruh isi tabel produk</t>
-  </si>
-  <si>
-    <t>tampilkan semua pesanan yang ada</t>
-  </si>
-  <si>
-    <t>ambil data lengkap dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>perlihatkan seluruh data pelanggan</t>
-  </si>
-  <si>
-    <t>tampilkan isi tabel produk secara lengkap</t>
-  </si>
-  <si>
-    <t>ambil semua informasi pesanan</t>
-  </si>
-  <si>
-    <t>tampilkan semua data detail_pesanan</t>
-  </si>
-  <si>
-    <t>ambil seluruh data dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>tampilkan data lengkap dari produk</t>
-  </si>
-  <si>
-    <t>ambil semua informasi dari tabel produk</t>
-  </si>
-  <si>
-    <t>lihat seluruh isi tabel pesanan</t>
-  </si>
-  <si>
-    <t>tunjukkan semua record di tabel detailpesanan</t>
-  </si>
-  <si>
-    <t>tampilkan semua entri di tabel pembayaran</t>
-  </si>
-  <si>
-    <t>dapatkan semua data pelanggan yang tersimpan</t>
-  </si>
-  <si>
-    <t>ambil semua produk yang ada di database</t>
-  </si>
-  <si>
-    <t>lihat semua pesanan yang tercatat</t>
-  </si>
-  <si>
-    <t>tampilkan seluruh detail pesanan</t>
-  </si>
-  <si>
-    <t>tampilkan semua data pembayaran yang ada</t>
-  </si>
-  <si>
     <t>SELECT * FROM $TABLE WHERE $CONDITION</t>
   </si>
   <si>
-    <t>tampilkan semua mahasiswa yang jurusannya teknik informatika</t>
-  </si>
-  <si>
-    <t>ambil data dosen yang bidang_keahliannya jaringan komputer</t>
-  </si>
-  <si>
-    <t>cari mata_kuliah dengan sks lebih dari 3</t>
-  </si>
-  <si>
-    <t>lihat kelas dengan kapasitas lebih dari 30 mahasiswa</t>
-  </si>
-  <si>
-    <t>tampilkan jadwal yang harinya senin</t>
-  </si>
-  <si>
-    <t>ambil pendaftaran_kelas yang id_mahasiswanya 101</t>
-  </si>
-  <si>
-    <t>cari nilai dengan nilai_huruf sama dengan a</t>
-  </si>
-  <si>
-    <t>tampilkan mahasiswa yang nimnya 123456789</t>
-  </si>
-  <si>
-    <t>lihat dosen yang namanya mengandung kata “sutrisno”</t>
-  </si>
-  <si>
-    <t>ambil mata_kuliah yang semesternya 2</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari akun dimana tipe_akun adalah aset</t>
-  </si>
-  <si>
-    <t>ambil data dari jurnal dengan tanggal sama dengan 2025-05-01</t>
-  </si>
-  <si>
-    <t>perlihatkan detail_jurnal yang id_jurnal-nya 10</t>
-  </si>
-  <si>
-    <t>cari pengguna dengan username sama dengan 'admin'</t>
-  </si>
-  <si>
-    <t>tampilkan buku_besar untuk id_akun 5 pada tanggal 2025-04-30</t>
-  </si>
-  <si>
-    <t>ambil data akun dengan kode_akun sama dengan '101'</t>
-  </si>
-  <si>
-    <t>lihat jurnal dengan deskripsi berisi kata 'penjualan'</t>
-  </si>
-  <si>
-    <t>tampilkan detail_jurnal dimana debit lebih besar dari 100000</t>
-  </si>
-  <si>
-    <t>perlihatkan pengguna yang perannya adalah akuntan</t>
-  </si>
-  <si>
-    <t>ambil buku_besar dengan saldo_debit lebih besar dari 5000000</t>
-  </si>
-  <si>
-    <t>tampilkan data pelanggan yang memiliki email tertentu</t>
-  </si>
-  <si>
-    <t>ambil semua kamar dengan status tersedia</t>
-  </si>
-  <si>
-    <t>perlihatkan reservasi yang dilakukan pada tanggal tertentu</t>
-  </si>
-  <si>
-    <t>tampilkan pembayaran dengan metode pembayaran transfer bank</t>
-  </si>
-  <si>
-    <t>ambil staf yang memiliki posisi sebagai resepsionis</t>
-  </si>
-  <si>
-    <t>perlihatkan kamar dengan harga per malam di atas 500000</t>
-  </si>
-  <si>
-    <t>tampilkan reservasi dengan tanggal checkin hari ini</t>
-  </si>
-  <si>
-    <t>ambil data pembayaran yang jumlah pembayarannya lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>perlihatkan pelanggan dengan nama yang mengandung kata "andi"</t>
-  </si>
-  <si>
-    <t>tampilkan semua kamar yang termasuk jenis kamar suite</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari produk dimana jumlah_stok lebih dari 50</t>
-  </si>
-  <si>
-    <t>ambil data dari pelanggan dimana nama_pelanggan adalah 'andi'</t>
-  </si>
-  <si>
-    <t>tampilkan semua pemasok dimana kontak mengandung 'gmail.com'</t>
-  </si>
-  <si>
-    <t>lihat data dari produk dimana harga kurang dari 1000000</t>
-  </si>
-  <si>
-    <t>tampilkan data pesananpembelian dimana tanggal_pesanan adalah '2024-05-01'</t>
-  </si>
-  <si>
-    <t>ambil semua data dari detailpesananpembelian dimana jumlah lebih dari 10</t>
-  </si>
-  <si>
-    <t>lihat semua pesananpenjualan dimana pelanggan_id sama dengan 3</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari produk dimana kategori_id adalah 2</t>
-  </si>
-  <si>
-    <t>ambil data dari detailpesananpenjualan dimana produk_id adalah 5</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari pemasok dimana nama_pemasok adalah 'pt sumber daya'</t>
-  </si>
-  <si>
-    <t>tampilkan data pegawai yang bernama budi</t>
-  </si>
-  <si>
-    <t>ambil semua data absensi pada tanggal 2024-05-01</t>
-  </si>
-  <si>
-    <t>lihat informasi gaji pegawai dengan pegawai_id 5</t>
-  </si>
-  <si>
-    <t>tampilkan semua pegawai yang bekerja di divisi_id 3</t>
-  </si>
-  <si>
-    <t>ambil data jabatan dengan nama_jabatan manager</t>
-  </si>
-  <si>
-    <t>lihat absensi pegawai dengan status sakit</t>
-  </si>
-  <si>
-    <t>tampilkan data gaji untuk bulan 3 dan tahun 2025</t>
-  </si>
-  <si>
-    <t>ambil pegawai yang masuk pada tanggal 2023-01-15</t>
-  </si>
-  <si>
-    <t>tampilkan semua divisi yang berlokasi di jakarta</t>
-  </si>
-  <si>
-    <t>lihat data pegawai dengan jenis_kelamin perempuan</t>
-  </si>
-  <si>
-    <t>tampilkan data pelanggan dengan nama_pelanggan = 'andi'</t>
-  </si>
-  <si>
-    <t>ambil semua produk yang harganya lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>tampilkan pesanan dengan status_pesanan = 'selesai'</t>
-  </si>
-  <si>
-    <t>ambil detail_pesanan dengan jumlah lebih dari 5</t>
-  </si>
-  <si>
-    <t>tampilkan produk yang stoknya kurang dari 10</t>
-  </si>
-  <si>
-    <t>ambil data pelanggan yang emailnya = 'budi@example.com'</t>
-  </si>
-  <si>
-    <t>tampilkan pesanan dengan id_pelanggan = 3</t>
-  </si>
-  <si>
-    <t>ambil detail_pesanan dengan id_produk = 7</t>
-  </si>
-  <si>
-    <t>tampilkan produk dengan nama_produk = 'laptop lenovo'</t>
-  </si>
-  <si>
-    <t>ambil semua pesanan dengan tanggal_pesanan = '2025-05-18'</t>
-  </si>
-  <si>
-    <t>tampilkan semua data dari tabel pelanggan dimana nama adalah 'andi'</t>
-  </si>
-  <si>
-    <t>ambil semua produk yang harga lebih dari 100000</t>
-  </si>
-  <si>
-    <t>tampilkan semua pesanan dimana id_pelanggan adalah 5</t>
-  </si>
-  <si>
-    <t>lihat semua detailpesanan dengan jumlah lebih dari 3</t>
-  </si>
-  <si>
-    <t>ambil data pembayaran dimana metode_pembayaran adalah 'transfer bank'</t>
-  </si>
-  <si>
-    <t>tampilkan pesanan dengan total_harga kurang dari 500000</t>
-  </si>
-  <si>
-    <t>cari produk yang stok sama dengan 0</t>
-  </si>
-  <si>
-    <t>tampilkan pelanggan yang alamatnya mengandung 'jakarta'</t>
-  </si>
-  <si>
-    <t>ambil semua data detailpesanan dimana id_produk adalah 2</t>
-  </si>
-  <si>
-    <t>lihat pembayaran dengan jumlah_bayar lebih dari 1000000</t>
-  </si>
-  <si>
     <t>SELECT $COLUMN FROM $TABLE</t>
   </si>
   <si>
-    <t>tampilkan nama dari mahasiswa</t>
-  </si>
-  <si>
-    <t>ambil email dari dosen</t>
-  </si>
-  <si>
-    <t>lihat nama_mata_kuliah dari mata_kuliah</t>
-  </si>
-  <si>
-    <t>tampilkan tahun_akademik dari kelas</t>
-  </si>
-  <si>
-    <t>ambil hari dari jadwal</t>
-  </si>
-  <si>
-    <t>lihat tanggal_pendaftaran dari pendaftaran_kelas</t>
-  </si>
-  <si>
-    <t>tampilkan nilai_angka dari nilai</t>
-  </si>
-  <si>
-    <t>ambil nim dari mahasiswa</t>
-  </si>
-  <si>
-    <t>lihat bidang_keahlian dari dosen</t>
-  </si>
-  <si>
-    <t>tampilkan sks dari mata_kuliah</t>
-  </si>
-  <si>
-    <t>tampilkan nama_akun dari tabel akun</t>
-  </si>
-  <si>
-    <t>ambil tanggal dari jurnal</t>
-  </si>
-  <si>
-    <t>perlihatkan kode_akun dari akun</t>
-  </si>
-  <si>
-    <t>ambil deskripsi dari tabel jurnal</t>
-  </si>
-  <si>
-    <t>tampilkan nama dari pengguna</t>
-  </si>
-  <si>
-    <t>lihat tipe_akun dari tabel akun</t>
-  </si>
-  <si>
-    <t>ambil username dari pengguna</t>
-  </si>
-  <si>
-    <t>tampilkan debit dari detail_jurnal</t>
-  </si>
-  <si>
-    <t>perlihatkan saldo_kredit dari buku_besar</t>
-  </si>
-  <si>
-    <t>ambil kredit dari detail_jurnal</t>
-  </si>
-  <si>
-    <t>tampilkan nama dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>ambil nomor_kamar dari tabel kamar</t>
-  </si>
-  <si>
-    <t>perlihatkan tanggal_checkin dari tabel reservasi</t>
-  </si>
-  <si>
-    <t>tampilkan metode_pembayaran dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>ambil email dari tabel staf</t>
-  </si>
-  <si>
-    <t>tampilkan nama_jenis dari tabel jeniskamar</t>
-  </si>
-  <si>
-    <t>ambil total_biaya dari tabel reservasi</t>
-  </si>
-  <si>
-    <t>tampilkan harga_per_malam dari tabel kamar</t>
-  </si>
-  <si>
-    <t>perlihatkan jumlah_pembayaran dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>ambil nomor_telepon dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>tampilkan nama_produk dari tabel produk</t>
-  </si>
-  <si>
-    <t>ambil nama_kategori dari kategori</t>
-  </si>
-  <si>
-    <t>lihat harga dari produk</t>
-  </si>
-  <si>
-    <t>tampilkan kontak dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>ambil tanggal_pesanan dari pesananpembelian</t>
-  </si>
-  <si>
-    <t>tampilkan nama_pemasok dari pemasok</t>
-  </si>
-  <si>
-    <t>lihat jumlah dari detailpesananpenjualan</t>
-  </si>
-  <si>
-    <t>ambil harga_satuan dari detailpesananpenjualan</t>
-  </si>
-  <si>
-    <t>tampilkan nama_pelanggan dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>ambil deskripsi dari produk</t>
-  </si>
-  <si>
-    <t>tampilkan nama dari pegawai</t>
-  </si>
-  <si>
-    <t>ambil alamat dari pegawai</t>
-  </si>
-  <si>
-    <t>lihat nama_jabatan dari jabatan</t>
-  </si>
-  <si>
-    <t>tampilkan gaji_pokok dari jabatan</t>
-  </si>
-  <si>
-    <t>ambil nama_divisi dari divisi</t>
-  </si>
-  <si>
-    <t>lihat status dari absensi</t>
-  </si>
-  <si>
-    <t>tampilkan tanggal dari absensi</t>
-  </si>
-  <si>
-    <t>ambil jumlah_gaji dari gaji</t>
-  </si>
-  <si>
-    <t>tampilkan bulan dari gaji</t>
-  </si>
-  <si>
-    <t>lihat lokasi dari divisi</t>
-  </si>
-  <si>
-    <t>ambil harga dari produk</t>
-  </si>
-  <si>
-    <t>tampilkan tanggal_pesanan dari pesanan</t>
-  </si>
-  <si>
-    <t>ambil jumlah dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>tampilkan status_pesanan dari pesanan</t>
-  </si>
-  <si>
-    <t>ambil stok dari produk</t>
-  </si>
-  <si>
-    <t>tampilkan email dari pelanggan</t>
-  </si>
-  <si>
-    <t>ambil harga_satuan dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>tampilkan nama_produk dari produk</t>
-  </si>
-  <si>
-    <t>ambil telepon dari pelanggan</t>
-  </si>
-  <si>
-    <t>tampilkan nama dan email dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>ambil nama_produk dan harga dari tabel produk</t>
-  </si>
-  <si>
-    <t>lihat tanggal_pesanan dan total_harga dari tabel pesanan</t>
-  </si>
-  <si>
-    <t>tampilkan jumlah dan sub_total dari tabel detailpesanan</t>
-  </si>
-  <si>
-    <t>ambil metode_pembayaran dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>ambil stok dari tabel produk</t>
-  </si>
-  <si>
-    <t>lihat id_pesanan dan id_pelanggan dari tabel pesanan</t>
-  </si>
-  <si>
-    <t>tampilkan tanggal_bayar dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>ambil harga_satuan dari tabel detailpesanan</t>
-  </si>
-  <si>
     <t>SELECT $COLUMN FROM $TABLE WHERE $CONDITION</t>
   </si>
   <si>
-    <t>tampilkan nama dan nim dari mahasiswa yang jurusannya teknik informatika</t>
-  </si>
-  <si>
-    <t>ambil email dosen yang bidang_keahliannya sistem informasi</t>
-  </si>
-  <si>
-    <t>lihat nama_mata_kuliah dari mata_kuliah yang sks-nya lebih dari 3</t>
-  </si>
-  <si>
-    <t>tampilkan kapasitas kelas yang tahun_akademiknya 2023/2024</t>
-  </si>
-  <si>
-    <t>ambil jam_mulai dari jadwal yang harinya rabu</t>
-  </si>
-  <si>
-    <t>lihat tanggal_pendaftaran dari pendaftaran_kelas yang id_mahasiswa 150</t>
-  </si>
-  <si>
-    <t>tampilkan nilai_angka dari nilai yang nilai_hurufnya sama dengan b</t>
-  </si>
-  <si>
-    <t>ambil alamat mahasiswa yang nimnya 20211001</t>
-  </si>
-  <si>
-    <t>lihat nip dosen yang namanya mengandung kata “wijaya”</t>
-  </si>
-  <si>
-    <t>tampilkan semester mata_kuliah yang kode_mata_kuliahnya seperti ‘MK-01%’</t>
-  </si>
-  <si>
-    <t>tampilkan nama_akun dari akun dimana tipe_akun adalah aset</t>
-  </si>
-  <si>
-    <t>ambil tanggal dari jurnal dengan id_pengguna sama dengan 3</t>
-  </si>
-  <si>
-    <t>perlihatkan debit dari detail_jurnal dimana id_jurnal sama dengan 10</t>
-  </si>
-  <si>
-    <t>ambil nama dari pengguna dengan peran sama dengan admin</t>
-  </si>
-  <si>
-    <t>tampilkan saldo_debit dari buku_besar dimana tanggal sama dengan 2025-05-01</t>
-  </si>
-  <si>
-    <t>ambil kode_akun dari akun dengan id_akun sama dengan 5</t>
-  </si>
-  <si>
-    <t>lihat deskripsi dari jurnal dimana tanggal lebih besar dari 2025-04-01</t>
-  </si>
-  <si>
-    <t>tampilkan kredit dari detail_jurnal dimana debit lebih besar dari 100000</t>
-  </si>
-  <si>
-    <t>perlihatkan username dari pengguna dengan nama sama dengan joko</t>
-  </si>
-  <si>
-    <t>ambil saldo_kredit dari buku_besar dimana id_akun sama dengan 7</t>
-  </si>
-  <si>
-    <t>tampilkan nama_produk dari produk dimana jumlah_stok lebih dari 100</t>
-  </si>
-  <si>
-    <t>ambil nama_pelanggan dari pelanggan dimana pelanggan_id sama dengan 5</t>
-  </si>
-  <si>
-    <t>lihat harga dari produk dimana kategori_id adalah 3</t>
-  </si>
-  <si>
-    <t>tampilkan tanggal_pesanan dari pesananpembelian dimana pemasok_id sama dengan 2</t>
-  </si>
-  <si>
-    <t>ambil jumlah dari detailpesananpembelian dimana produk_id adalah 10</t>
-  </si>
-  <si>
-    <t>tampilkan nama_pemasok dari pemasok dimana kontak mengandung '0812'</t>
-  </si>
-  <si>
-    <t>lihat harga_satuan dari detailpesananpenjualan dimana pesanan_penjualan_id sama dengan 7</t>
-  </si>
-  <si>
-    <t>ambil nama_kategori dari kategori dimana kategori_id adalah 1</t>
-  </si>
-  <si>
-    <t>tampilkan deskripsi dari produk dimana produk_id sama dengan 15</t>
-  </si>
-  <si>
-    <t>ambil jumlah dari detailpesananpenjualan dimana produk_id adalah 4</t>
-  </si>
-  <si>
-    <t>tampilkan nama dan alamat dari pegawai yang jabatan_id nya 2</t>
-  </si>
-  <si>
-    <t>ambil tanggal dan status dari absensi dimana pegawai_id 5</t>
-  </si>
-  <si>
-    <t>lihat nama_jabatan dari jabatan yang gaji_pokok lebih besar dari 5000000</t>
-  </si>
-  <si>
-    <t>tampilkan nama_divisi dan lokasi dari divisi yang lokasi nya jakarta</t>
-  </si>
-  <si>
-    <t>ambil jumlah_gaji dari gaji untuk pegawai_id 3 dan bulan 4</t>
-  </si>
-  <si>
-    <t>lihat email dari pegawai yang jenis_kelamin perempuan</t>
-  </si>
-  <si>
-    <t>tampilkan nama dan no_telepon dari pegawai yang tanggal_masuk setelah 2022-01-01</t>
-  </si>
-  <si>
-    <t>ambil status dari absensi pada tanggal 2024-05-01</t>
-  </si>
-  <si>
-    <t>lihat nama_jabatan dari jabatan dengan nama_jabatan manager</t>
-  </si>
-  <si>
-    <t>tampilkan bulan dan tahun dari gaji yang jumlah_gaji lebih dari 10000000</t>
-  </si>
-  <si>
-    <t>tampilkan nama_pelanggan dari pelanggan dimana id_pelanggan sama dengan 1</t>
-  </si>
-  <si>
-    <t>ambil harga dari produk dimana stok lebih dari 10</t>
-  </si>
-  <si>
-    <t>tampilkan status_pesanan dari pesanan dimana id_pesanan sama dengan 5</t>
-  </si>
-  <si>
-    <t>ambil jumlah dari detail_pesanan dimana id_pesanan sama dengan 3</t>
-  </si>
-  <si>
-    <t>tampilkan email dari pelanggan dimana nama_pelanggan sama dengan 'budi'</t>
-  </si>
-  <si>
-    <t>ambil nama_produk dari produk dimana harga kurang dari 2000000</t>
-  </si>
-  <si>
-    <t>tampilkan telepon dari pelanggan dimana id_pelanggan sama dengan 2</t>
-  </si>
-  <si>
-    <t>ambil harga_satuan dari detail_pesanan dimana id_produk sama dengan 4</t>
-  </si>
-  <si>
-    <t>tampilkan tanggal_pesanan dari pesanan dimana status_pesanan sama dengan 'proses'</t>
-  </si>
-  <si>
-    <t>ambil stok dari produk dimana nama_produk sama dengan 'hp samsung'</t>
-  </si>
-  <si>
-    <t>tampilkan nama dan email dari tabel pelanggan dimana id_pelanggan sama dengan 10</t>
-  </si>
-  <si>
-    <t>ambil nama_produk dan harga dari tabel produk dimana stok lebih besar dari 5</t>
-  </si>
-  <si>
-    <t>lihat tanggal_pesanan dan total_harga dari tabel pesanan dimana id_pelanggan sama dengan 3</t>
-  </si>
-  <si>
-    <t>tampilkan jumlah dan sub_total dari tabel detailpesanan dimana id_pesanan sama dengan 7</t>
-  </si>
-  <si>
-    <t>ambil metode_pembayaran dari tabel pembayaran dimana jumlah_bayar lebih dari 100000</t>
-  </si>
-  <si>
-    <t>tampilkan nama dari tabel pelanggan dimana alamat mengandung 'bandung'</t>
-  </si>
-  <si>
-    <t>ambil stok dari tabel produk dimana harga kurang dari 50000</t>
-  </si>
-  <si>
-    <t>lihat id_pesanan dan id_pelanggan dari tabel pesanan dimana total_harga lebih dari 200000</t>
-  </si>
-  <si>
-    <t>tampilkan tanggal_bayar dari tabel pembayaran dimana metode_pembayaran adalah 'kartu kredit'</t>
-  </si>
-  <si>
-    <t>ambil harga_satuan dari tabel detailpesanan dimana jumlah sama dengan 2</t>
-  </si>
-  <si>
     <t>SELECT $AGG $COLUMN FROM $TABLE</t>
   </si>
   <si>
-    <t>hitung jumlah id_mahasiswa dari table mahasiswa</t>
-  </si>
-  <si>
-    <t>hitung total kapasitas dari table kelas</t>
-  </si>
-  <si>
-    <t>cari rata-rata nilai_angka dari table nilai</t>
-  </si>
-  <si>
-    <t>cari nilai maksimal sks dari table mata_kuliah</t>
-  </si>
-  <si>
-    <t>cari nilai minimal sks dari table mata_kuliah</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_dosen dari table dosen</t>
-  </si>
-  <si>
-    <t>hitung total id_pendaftaran dari table pendaftaran_kelas</t>
-  </si>
-  <si>
-    <t>cari rata-rata kapasitas dari table kelas</t>
-  </si>
-  <si>
-    <t>cari nilai maksimal nilai_angka dari table nilai</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_jadwal dari table jadwal</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_akun dari akun</t>
-  </si>
-  <si>
-    <t>cari rata-rata debit dari detail_jurnal</t>
-  </si>
-  <si>
-    <t>tampilkan nilai maksimum saldo_debit dari buku_besar</t>
-  </si>
-  <si>
-    <t>hitung total kredit dari detail_jurnal</t>
-  </si>
-  <si>
-    <t>cari nilai minimum tanggal dari jurnal</t>
-  </si>
-  <si>
-    <t>hitung jumlah pengguna dengan menghitung id_pengguna</t>
-  </si>
-  <si>
-    <t>tampilkan rata-rata saldo_kredit dari buku_besar</t>
-  </si>
-  <si>
-    <t>cari total debit dari detail_jurnal</t>
-  </si>
-  <si>
-    <t>hitung maksimum kode_akun dari akun</t>
-  </si>
-  <si>
-    <t>tampilkan nilai minimum saldo_debit dari buku_besar</t>
-  </si>
-  <si>
-    <t>hitung jumlah pelanggan dari tabel pelanggan</t>
-  </si>
-  <si>
-    <t>jumlahkan total_biaya dari tabel reservasi</t>
-  </si>
-  <si>
-    <t>hitung jumlah kamar dari tabel kamar</t>
-  </si>
-  <si>
-    <t>ambil nilai rata-rata harga_per_malam dari tabel kamar</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum jumlah_pembayaran dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>cari nilai minimum total_biaya dari tabel reservasi</t>
-  </si>
-  <si>
-    <t>hitung jumlah pembayaran dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>jumlahkan jumlah_pembayaran dari tabel pembayaran</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum total_biaya dari tabel reservasi</t>
-  </si>
-  <si>
-    <t>hitung jumlah semua produk dari tabel produk</t>
-  </si>
-  <si>
-    <t>hitung total harga dari produk</t>
-  </si>
-  <si>
-    <t>cari rata-rata harga_satuan dari detailpesananpenjualan</t>
-  </si>
-  <si>
-    <t>ambil jumlah seluruh pesanan dari pesananpembelian</t>
-  </si>
-  <si>
-    <t>cari total jumlah dari detailpesananpembelian</t>
-  </si>
-  <si>
-    <t>cari harga tertinggi dari produk</t>
-  </si>
-  <si>
-    <t>cari jumlah stok terendah dari produk</t>
-  </si>
-  <si>
-    <t>hitung total jumlah produk dari detailpesananpenjualan</t>
-  </si>
-  <si>
-    <t>ambil rata-rata jumlah dari detailpesananpembelian</t>
-  </si>
-  <si>
-    <t>hitung jumlah pegawai dari tabel pegawai</t>
-  </si>
-  <si>
-    <t>total seluruh gaji dari tabel gaji</t>
-  </si>
-  <si>
-    <t>rata-rata gaji_pokok dari tabel jabatan</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum jumlah_gaji dari tabel gaji</t>
-  </si>
-  <si>
-    <t>cari nilai minimum jumlah_gaji dari tabel gaji</t>
-  </si>
-  <si>
-    <t>hitung jumlah absensi dari tabel absensi</t>
-  </si>
-  <si>
-    <t>rata-rata gaji_pokok dari jabatan</t>
-  </si>
-  <si>
-    <t>hitung jumlah nama_jabatan dari tabel jabatan</t>
-  </si>
-  <si>
-    <t>total jumlah_gaji dari gaji</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum gaji_pokok dari tabel jabatan</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_pelanggan dari pelanggan</t>
-  </si>
-  <si>
-    <t>cari rata-rata harga dari produk</t>
-  </si>
-  <si>
-    <t>hitung total jumlah dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum harga_satuan dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>cari nilai minimum stok dari produk</t>
-  </si>
-  <si>
-    <t>hitung jumlah pesanan dari tabel pesanan</t>
-  </si>
-  <si>
-    <t>cari rata-rata harga_satuan dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>hitung total stok dari produk</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum jumlah dari detail_pesanan</t>
-  </si>
-  <si>
-    <t>cari nilai minimum harga dari produk</t>
-  </si>
-  <si>
-    <t>cari total stok dari tabel produk</t>
-  </si>
-  <si>
-    <t>hitung total harga dari tabel pesanan</t>
-  </si>
-  <si>
-    <t>cari jumlah seluruh sub_total dari tabel detailpesanan</t>
-  </si>
-  <si>
-    <t>ambil rata-rata harga dari tabel produk</t>
-  </si>
-  <si>
-    <t>cari total jumlah dari tabel detailpesanan</t>
-  </si>
-  <si>
-    <t>hitung rata-rata total_harga dari tabel pesanan</t>
-  </si>
-  <si>
-    <t>ambil jumlah harga_satuan dari tabel detailpesanan</t>
-  </si>
-  <si>
-    <t>hitung rata-rata jumlah_bayar dari tabel pembayaran</t>
-  </si>
-  <si>
     <t>SELECT $AGG $COLUMN FROM $TABLE GROUP BY $COLUMN HAVING $CONDITION</t>
   </si>
   <si>
-    <t>cari jumlah mahasiswa di setiap jurusan yang jumlahnya lebih dari 100</t>
-  </si>
-  <si>
-    <t>hitung total kelas per mata_kuliah yang lebih dari 3 kelas</t>
-  </si>
-  <si>
-    <t>cari rata-rata kapasitas per kelas yang lebih besar dari 40</t>
-  </si>
-  <si>
-    <t>cari jumlah dosen berdasarkan bidang_keahlian yang jumlahnya lebih dari 2</t>
-  </si>
-  <si>
-    <t>hitung jumlah pendaftaran per id_kelas yang lebih dari 10</t>
-  </si>
-  <si>
-    <t>cari jumlah jadwal per hari yang lebih dari 5</t>
-  </si>
-  <si>
-    <t>hitung rata-rata nilai_angka per id_kelas yang lebih besar dari 70</t>
-  </si>
-  <si>
-    <t>cari jumlah mahasiswa per alamat yang jumlahnya lebih dari 20</t>
-  </si>
-  <si>
-    <t>hitung jumlah mata_kuliah berdasarkan semester yang lebih dari 4</t>
-  </si>
-  <si>
-    <t>cari rata-rata sks per semester yang lebih dari 2</t>
-  </si>
-  <si>
-    <t>hitung total debit dari detail_jurnal group berdasarkan id_akun dengan syarat total debit lebih dari 100000</t>
-  </si>
-  <si>
-    <t>cari rata-rata saldo_kredit dari buku_besar group berdasarkan id_akun dengan saldo_kredit rata-rata di atas 500000</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_jurnal dari detail_jurnal group berdasarkan id_akun dengan jumlah lebih dari 5</t>
-  </si>
-  <si>
-    <t>tampilkan maksimum saldo_debit dari buku_besar group berdasarkan tanggal dengan syarat maksimum saldo_debit di atas 1000000</t>
-  </si>
-  <si>
-    <t>cari total kredit dari detail_jurnal group berdasarkan id_jurnal dengan syarat total kredit lebih dari 250000</t>
-  </si>
-  <si>
-    <t>hitung rata-rata debit dari detail_jurnal group berdasarkan id_akun dengan debit rata-rata lebih besar dari 10000</t>
-  </si>
-  <si>
-    <t>tampilkan total saldo_kredit dari buku_besar group berdasarkan tanggal dengan syarat total saldo_kredit di atas 300000</t>
-  </si>
-  <si>
-    <t>hitung jumlah pengguna dari pengguna group berdasarkan peran dengan jumlah lebih dari 2</t>
-  </si>
-  <si>
-    <t>tampilkan maksimum debit dari detail_jurnal group berdasarkan id_jurnal dengan syarat maksimum debit lebih dari 200000</t>
-  </si>
-  <si>
-    <t>cari rata-rata saldo_debit dari buku_besar group berdasarkan id_akun dengan saldo_debit rata-rata lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah reservasi dari tabel reservasi berdasarkan tanggal_checkin yang memiliki total_biaya lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>jumlahkan jumlah_pembayaran dari tabel pembayaran berdasarkan metode_pembayaran yang totalnya lebih dari 500000</t>
-  </si>
-  <si>
-    <t>hitung jumlah kamar dari tabel kamar berdasarkan id_jenis_kamar yang memiliki lebih dari 5 kamar</t>
-  </si>
-  <si>
-    <t>hitung jumlah staf dari tabel staf berdasarkan posisi yang jumlahnya lebih dari 2 orang</t>
-  </si>
-  <si>
-    <t>hitung jumlah pelanggan dari tabel pelanggan berdasarkan email yang digunakan lebih dari satu kali</t>
-  </si>
-  <si>
-    <t>jumlahkan total_biaya dari tabel reservasi berdasarkan tanggal_reservasi yang melebihi 2000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah pembayaran dari tabel pembayaran berdasarkan tanggal_pembayaran yang lebih dari 3 transaksi</t>
-  </si>
-  <si>
-    <t>jumlahkan harga_per_malam dari tabel kamar berdasarkan status yang totalnya lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah reservasi dari tabel reservasi berdasarkan id_kamar yang memiliki lebih dari 2 reservasi</t>
-  </si>
-  <si>
-    <t>jumlahkan jumlah_pembayaran dari tabel pembayaran berdasarkan id_reservasi yang totalnya lebih dari 1500000</t>
-  </si>
-  <si>
-    <t>hitung total jumlah dari detailpesananpenjualan dikelompokkan berdasarkan produk_id yang jumlahnya lebih dari 50</t>
-  </si>
-  <si>
-    <t>cari rata-rata harga dari produk dikelompokkan berdasarkan kategori_id yang rata-ratanya di atas 1000000</t>
-  </si>
-  <si>
-    <t>ambil jumlah pesanan dari pesananpenjualan dikelompokkan berdasarkan pelanggan_id yang jumlahnya lebih dari 3</t>
-  </si>
-  <si>
-    <t>hitung total jumlah dari detailpesananpembelian dikelompokkan berdasarkan produk_id dengan total lebih dari 20</t>
-  </si>
-  <si>
-    <t>cari total harga_satuan dari detailpesananpenjualan dikelompokkan berdasarkan pesanan_penjualan_id yang totalnya lebih dari 500000</t>
-  </si>
-  <si>
-    <t>hitung jumlah stok dari produk dikelompokkan berdasarkan kategori_id dengan stok lebih dari 100</t>
-  </si>
-  <si>
-    <t>ambil rata-rata harga dari produk dikelompokkan berdasarkan kategori_id yang rata-ratanya kurang dari 500000</t>
-  </si>
-  <si>
-    <t>hitung total jumlah dari detailpesananpembelian dikelompokkan berdasarkan pesanan_pembelian_id yang jumlahnya lebih dari 5</t>
-  </si>
-  <si>
-    <t>cari jumlah pesanan dari pesananpembelian dikelompokkan berdasarkan pemasok_id yang jumlahnya di atas 2</t>
-  </si>
-  <si>
-    <t>ambil total harga_satuan dari detailpesananpembelian dikelompokkan berdasarkan produk_id dengan total lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah pegawai dari tabel pegawai berdasarkan divisi_id yang memiliki lebih dari 5 pegawai</t>
-  </si>
-  <si>
-    <t>total jumlah_gaji dari gaji berdasarkan pegawai_id yang totalnya lebih dari 10000000</t>
-  </si>
-  <si>
-    <t>rata-rata gaji_pokok dari jabatan berdasarkan nama_jabatan yang rata-ratanya lebih dari 5000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah absensi dari tabel absensi berdasarkan status yang jumlahnya lebih dari 10</t>
-  </si>
-  <si>
-    <t>total jumlah_gaji dari tabel gaji berdasarkan bulan yang totalnya lebih dari 15000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah pegawai dari tabel pegawai berdasarkan jabatan_id yang memiliki lebih dari 3 orang</t>
-  </si>
-  <si>
-    <t>rata-rata jumlah_gaji dari tabel gaji berdasarkan tahun yang rata-ratanya di atas 7000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah absensi dari tabel absensi berdasarkan pegawai_id yang memiliki lebih dari 20 absensi</t>
-  </si>
-  <si>
-    <t>total gaji_pokok dari tabel jabatan berdasarkan nama_jabatan yang totalnya lebih dari 8000000</t>
-  </si>
-  <si>
-    <t>hitung jumlah pegawai dari tabel pegawai berdasarkan jenis_kelamin yang jumlahnya lebih dari 5</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_pesanan dari detail_pesanan kelompok berdasarkan id_pesanan dengan jumlah lebih dari 5</t>
-  </si>
-  <si>
-    <t>cari total harga_satuan dari detail_pesanan kelompok berdasarkan id_produk dengan total harga_satuan lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>hitung rata-rata harga dari produk kelompok berdasarkan nama_produk dengan rata-rata harga kurang dari 5000000</t>
-  </si>
-  <si>
-    <t>cari jumlah id_pelanggan dari pelanggan kelompok berdasarkan alamat dengan jumlah id_pelanggan lebih dari 10</t>
-  </si>
-  <si>
-    <t>hitung total jumlah dari detail_pesanan kelompok berdasarkan id_produk dengan total jumlah lebih dari 20</t>
-  </si>
-  <si>
-    <t>cari nilai maksimum stok dari produk kelompok berdasarkan nama_produk dengan stok lebih dari 50</t>
-  </si>
-  <si>
-    <t>hitung jumlah id_pesanan dari detail_pesanan kelompok berdasarkan id_produk dengan jumlah id_pesanan lebih dari 3</t>
-  </si>
-  <si>
-    <t>cari total harga_satuan dari detail_pesanan kelompok berdasarkan id_pesanan dengan total harga_satuan lebih dari 500000</t>
-  </si>
-  <si>
-    <t>hitung rata-rata harga dari produk kelompok berdasarkan nama_produk dengan rata-rata harga lebih dari 2000000</t>
-  </si>
-  <si>
-    <t>cari jumlah id_pelanggan dari pelanggan kelompok berdasarkan email dengan jumlah id_pelanggan lebih dari 1</t>
-  </si>
-  <si>
-    <t>hitung jumlah pesanan dari tabel pesanan group by id_pelanggan dimana total_harga lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>cari total jumlah dari detailpesanan group by id_produk dimana sub_total lebih dari 500000</t>
-  </si>
-  <si>
-    <t>hitung rata-rata harga dari produk group by nama_produk dimana harga lebih dari 100000</t>
-  </si>
-  <si>
-    <t>ambil jumlah pembayaran dari pembayaran group by metode_pembayaran dimana jumlah_bayar lebih dari 200000</t>
-  </si>
-  <si>
-    <t>hitung total stok dari produk group by nama_produk dimana stok kurang dari 10</t>
-  </si>
-  <si>
-    <t>cari jumlah pesanan dari pesanan group by tanggal_pesanan dimana total_harga kurang dari 500000</t>
-  </si>
-  <si>
-    <t>hitung rata-rata jumlah dari detailpesanan group by id_pesanan dimana jumlah lebih dari 5</t>
-  </si>
-  <si>
-    <t>ambil jumlah pembayaran dari pembayaran group by tanggal_bayar dimana jumlah_bayar lebih dari 1000000</t>
-  </si>
-  <si>
-    <t>hitung total harga dari pesanan group by id_pelanggan dimana total_harga lebih dari 2000000</t>
-  </si>
-  <si>
-    <t>cari rata-rata harga dari produk group by id_produk dimana harga kurang dari 75000</t>
-  </si>
-  <si>
     <t>akademik_1.json</t>
   </si>
   <si>
@@ -1287,6 +78,1218 @@
   </si>
   <si>
     <t>penjualan_1.json</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data mahasiswa.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data mahasiswa. =&gt; tampilkan semua data mahasiswa</t>
+  </si>
+  <si>
+    <t>Ambil seluruh informasi dari tabel dosen.</t>
+  </si>
+  <si>
+    <t>Lihat semua mata kuliah yang tersedia.</t>
+  </si>
+  <si>
+    <t>Tampilkan daftar kelas lengkap.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh jadwal perkuliahan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua pendaftaran kelas mahasiswa.</t>
+  </si>
+  <si>
+    <t>Lihat seluruh nilai yang tercatat.</t>
+  </si>
+  <si>
+    <t>Ambil semua data dari tabel mahasiswa.</t>
+  </si>
+  <si>
+    <t>Tampilkan seluruh informasi dosen pengajar.</t>
+  </si>
+  <si>
+    <t>Lihat daftar semua mata kuliah yang terdaftar.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari tabel akun.</t>
+  </si>
+  <si>
+    <t>Ambil semua informasi dari akun.</t>
+  </si>
+  <si>
+    <t>Perlihatkan seluruh isi tabel jurnal.</t>
+  </si>
+  <si>
+    <t>Lihat semua data pada tabel detail jurnal.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua kolom dari tabel pengguna.</t>
+  </si>
+  <si>
+    <t>Ambil data lengkap dari tabel buku besar.</t>
+  </si>
+  <si>
+    <t>Berikan semua baris dari tabel akun.</t>
+  </si>
+  <si>
+    <t>Tampilkan seluruh record pada tabel jurnal.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua entri dalam tabel pengguna.</t>
+  </si>
+  <si>
+    <t>Perlihatkan data lengkap dari buku besar.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh isi tabel kamar.</t>
+  </si>
+  <si>
+    <t>Perlihatkan semua reservasi yang ada.</t>
+  </si>
+  <si>
+    <t>Dapatkan data lengkap dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Tampilkan seluruh data staf hotel.</t>
+  </si>
+  <si>
+    <t>Ambil semua informasi dari jeniskamar.</t>
+  </si>
+  <si>
+    <t>Tampilkan seluruh record dari tabel reservasi.</t>
+  </si>
+  <si>
+    <t>Perlihatkan data lengkap semua kamar.</t>
+  </si>
+  <si>
+    <t>Ambil semua data pelanggan yang tersimpan.</t>
+  </si>
+  <si>
+    <t>Tampilkan seluruh informasi pembayaran.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari produk.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh isi tabel kategori.</t>
+  </si>
+  <si>
+    <t>Lihat data lengkap dari pesananpembelian.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua baris pada tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil semua data dari detailpesananpenjualan.</t>
+  </si>
+  <si>
+    <t>Tampilkan isi lengkap tabel pemasok.</t>
+  </si>
+  <si>
+    <t>Lihat semua data yang ada di detailpesananpembelian.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh informasi dari tabel pesananpenjualan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua record dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Lihat data lengkap yang ada di tabel kategori.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari pegawai.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh informasi dari jabatan.</t>
+  </si>
+  <si>
+    <t>Lihat semua entri di divisi.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua absensi yang tercatat.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh data gaji karyawan.</t>
+  </si>
+  <si>
+    <t>Tampilkan data lengkap pegawai.</t>
+  </si>
+  <si>
+    <t>Lihat seluruh daftar jabatan yang ada.</t>
+  </si>
+  <si>
+    <t>Ambil semua data divisi di perusahaan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua record absensi.</t>
+  </si>
+  <si>
+    <t>Lihat seluruh data gaji bulanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh isi tabel produk.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua pesanan yang ada.</t>
+  </si>
+  <si>
+    <t>Ambil data lengkap dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Perlihatkan seluruh data pelanggan.</t>
+  </si>
+  <si>
+    <t>Tampilkan isi tabel produk secara lengkap.</t>
+  </si>
+  <si>
+    <t>Ambil semua informasi pesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data detail pesanan.</t>
+  </si>
+  <si>
+    <t>Ambil seluruh data dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Tampilkan data lengkap dari produk.</t>
+  </si>
+  <si>
+    <t>Ambil semua informasi dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Lihat seluruh isi tabel pesanan.</t>
+  </si>
+  <si>
+    <t>Tunjukkan semua record di tabel detailpesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua entri di tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Dapatkan semua data pelanggan yang tersimpan.</t>
+  </si>
+  <si>
+    <t>Ambil semua produk yang ada di database.</t>
+  </si>
+  <si>
+    <t>Lihat semua pesanan yang tercatat.</t>
+  </si>
+  <si>
+    <t>Tampilkan seluruh detail pesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data pembayaran yang ada.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua mahasiswa yang jurusannya teknik informatika.</t>
+  </si>
+  <si>
+    <t>Ambil data dosen yang bidang keahliannya jaringan komputer.</t>
+  </si>
+  <si>
+    <t>Cari mata kuliah dengan sks lebih dari 3.</t>
+  </si>
+  <si>
+    <t>Lihat kelas dengan kapasitas lebih dari 30 mahasiswa.</t>
+  </si>
+  <si>
+    <t>Tampilkan jadwal yang harinya senin.</t>
+  </si>
+  <si>
+    <t>Ambil pendaftaran kelas yang id mahasiswanya 101.</t>
+  </si>
+  <si>
+    <t>Cari nilai dengan nilai huruf sama dengan a.</t>
+  </si>
+  <si>
+    <t>Tampilkan mahasiswa yang nimnya 123456789.</t>
+  </si>
+  <si>
+    <t>Lihat dosen yang namanya mengandung kata “sutrisno”.</t>
+  </si>
+  <si>
+    <t>Ambil mata kuliah yang semesternya 2.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari akun dimana tipe akun adalah aset.</t>
+  </si>
+  <si>
+    <t>Ambil data dari jurnal dengan tanggal sama dengan 2025-05-01.</t>
+  </si>
+  <si>
+    <t>Perlihatkan detail jurnal yang id jurnal-nya 10.</t>
+  </si>
+  <si>
+    <t>Cari pengguna dengan username sama dengan 'admin'.</t>
+  </si>
+  <si>
+    <t>Tampilkan buku besar untuk id akun 5 pada tanggal 2025-04-30.</t>
+  </si>
+  <si>
+    <t>Ambil data akun dengan kode akun sama dengan '101'.</t>
+  </si>
+  <si>
+    <t>Lihat jurnal dengan deskripsi berisi kata 'penjualan'.</t>
+  </si>
+  <si>
+    <t>Tampilkan detail jurnal dimana debit lebih besar dari 100000.</t>
+  </si>
+  <si>
+    <t>Perlihatkan pengguna yang perannya adalah akuntan.</t>
+  </si>
+  <si>
+    <t>Ambil buku besar dengan saldo debit lebih besar dari 5000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan data pelanggan yang memiliki email tertentu.</t>
+  </si>
+  <si>
+    <t>Ambil semua kamar dengan status tersedia.</t>
+  </si>
+  <si>
+    <t>Perlihatkan reservasi yang dilakukan pada tanggal tertentu.</t>
+  </si>
+  <si>
+    <t>Tampilkan pembayaran dengan metode pembayaran transfer bank.</t>
+  </si>
+  <si>
+    <t>Ambil staf yang memiliki posisi sebagai resepsionis.</t>
+  </si>
+  <si>
+    <t>Perlihatkan kamar dengan harga per malam di atas 500000.</t>
+  </si>
+  <si>
+    <t>Tampilkan reservasi dengan tanggal checkin hari ini.</t>
+  </si>
+  <si>
+    <t>Ambil data pembayaran yang jumlah pembayarannya lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Perlihatkan pelanggan dengan nama yang mengandung kata "andi".</t>
+  </si>
+  <si>
+    <t>Tampilkan semua kamar yang termasuk jenis kamar suite.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari produk dimana jumlah stok lebih dari 50.</t>
+  </si>
+  <si>
+    <t>Ambil data dari pelanggan dimana nama pelanggan adalah 'andi'.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua pemasok dimana kontak mengandung 'gmail.com'.</t>
+  </si>
+  <si>
+    <t>Lihat data dari produk dimana harga kurang dari 1000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan data pesananpembelian dimana tanggal pesanan adalah '2024-05-01'.</t>
+  </si>
+  <si>
+    <t>Ambil semua data dari detailpesananpembelian dimana jumlah lebih dari 10.</t>
+  </si>
+  <si>
+    <t>Lihat semua pesananpenjualan dimana pelanggan id sama dengan 3.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari produk dimana kategori id adalah 2.</t>
+  </si>
+  <si>
+    <t>Ambil data dari detailpesananpenjualan dimana produk id adalah 5.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari pemasok dimana nama pemasok adalah 'pt sumber daya'.</t>
+  </si>
+  <si>
+    <t>Tampilkan data pegawai yang bernama budi.</t>
+  </si>
+  <si>
+    <t>Ambil semua data absensi pada tanggal 2024-05-01.</t>
+  </si>
+  <si>
+    <t>Lihat informasi gaji pegawai dengan pegawai id 5.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua pegawai yang bekerja di divisi id 3.</t>
+  </si>
+  <si>
+    <t>Ambil data jabatan dengan nama jabatan manager.</t>
+  </si>
+  <si>
+    <t>Lihat absensi pegawai dengan status sakit.</t>
+  </si>
+  <si>
+    <t>Tampilkan data gaji untuk bulan 3 dan tahun 2025.</t>
+  </si>
+  <si>
+    <t>Ambil pegawai yang masuk pada tanggal 2023-01-15.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua divisi yang berlokasi di jakarta.</t>
+  </si>
+  <si>
+    <t>Lihat data pegawai dengan jenis kelamin perempuan.</t>
+  </si>
+  <si>
+    <t>Tampilkan data pelanggan dengan nama pelanggan = 'andi'.</t>
+  </si>
+  <si>
+    <t>Ambil semua produk yang harganya lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan pesanan dengan status pesanan = 'selesai'.</t>
+  </si>
+  <si>
+    <t>Ambil detail pesanan dengan jumlah lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Tampilkan produk yang stoknya kurang dari 10.</t>
+  </si>
+  <si>
+    <t>Ambil data pelanggan yang emailnya = 'budi@example.com'.</t>
+  </si>
+  <si>
+    <t>Tampilkan pesanan dengan id pelanggan = 3.</t>
+  </si>
+  <si>
+    <t>Ambil detail pesanan dengan id produk = 7.</t>
+  </si>
+  <si>
+    <t>Tampilkan produk dengan nama produk = 'laptop lenovo'.</t>
+  </si>
+  <si>
+    <t>Ambil semua pesanan dengan tanggal pesanan = '2025-05-18'.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua data dari tabel pelanggan dimana nama adalah 'andi'.</t>
+  </si>
+  <si>
+    <t>Ambil semua produk yang harga lebih dari 100000.</t>
+  </si>
+  <si>
+    <t>Tampilkan semua pesanan dimana id pelanggan adalah 5.</t>
+  </si>
+  <si>
+    <t>Lihat semua detailpesanan dengan jumlah lebih dari 3.</t>
+  </si>
+  <si>
+    <t>Ambil data pembayaran dimana metode pembayaran adalah 'transfer bank'.</t>
+  </si>
+  <si>
+    <t>Tampilkan pesanan dengan total harga kurang dari 500000.</t>
+  </si>
+  <si>
+    <t>Cari produk yang stok sama dengan 0.</t>
+  </si>
+  <si>
+    <t>Tampilkan pelanggan yang alamatnya mengandung 'jakarta'.</t>
+  </si>
+  <si>
+    <t>Ambil semua data detailpesanan dimana id produk adalah 2.</t>
+  </si>
+  <si>
+    <t>Lihat pembayaran dengan jumlah bayar lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dari mahasiswa.</t>
+  </si>
+  <si>
+    <t>Ambil email dari dosen.</t>
+  </si>
+  <si>
+    <t>Lihat nama mata kuliah dari mata kuliah.</t>
+  </si>
+  <si>
+    <t>Tampilkan tahun akademik dari kelas.</t>
+  </si>
+  <si>
+    <t>Ambil hari dari jadwal.</t>
+  </si>
+  <si>
+    <t>Lihat tanggal pendaftaran dari pendaftaran kelas.</t>
+  </si>
+  <si>
+    <t>Tampilkan nilai angka dari nilai.</t>
+  </si>
+  <si>
+    <t>Ambil nim dari mahasiswa.</t>
+  </si>
+  <si>
+    <t>Lihat bidang keahlian dari dosen.</t>
+  </si>
+  <si>
+    <t>Tampilkan sks dari mata kuliah.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama akun dari tabel akun.</t>
+  </si>
+  <si>
+    <t>Ambil tanggal dari jurnal.</t>
+  </si>
+  <si>
+    <t>Perlihatkan kode akun dari akun.</t>
+  </si>
+  <si>
+    <t>Ambil deskripsi dari tabel jurnal.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dari pengguna.</t>
+  </si>
+  <si>
+    <t>Lihat tipe akun dari tabel akun.</t>
+  </si>
+  <si>
+    <t>Ambil username dari pengguna.</t>
+  </si>
+  <si>
+    <t>Tampilkan debit dari detail jurnal.</t>
+  </si>
+  <si>
+    <t>Perlihatkan saldo kredit dari buku besar.</t>
+  </si>
+  <si>
+    <t>Ambil kredit dari detail jurnal.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil nomor kamar dari tabel kamar.</t>
+  </si>
+  <si>
+    <t>Perlihatkan tanggal checkin dari tabel reservasi.</t>
+  </si>
+  <si>
+    <t>Tampilkan metode pembayaran dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Ambil email dari tabel staf.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama jenis dari tabel jeniskamar.</t>
+  </si>
+  <si>
+    <t>Ambil total biaya dari tabel reservasi.</t>
+  </si>
+  <si>
+    <t>Tampilkan harga per malam dari tabel kamar.</t>
+  </si>
+  <si>
+    <t>Perlihatkan jumlah pembayaran dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Ambil nomor telepon dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama produk dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Ambil nama kategori dari kategori.</t>
+  </si>
+  <si>
+    <t>Lihat harga dari produk.</t>
+  </si>
+  <si>
+    <t>Tampilkan kontak dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil tanggal pesanan dari pesananpembelian.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama pemasok dari pemasok.</t>
+  </si>
+  <si>
+    <t>Lihat jumlah dari detailpesananpenjualan.</t>
+  </si>
+  <si>
+    <t>Ambil harga satuan dari detailpesananpenjualan.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama pelanggan dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil deskripsi dari produk.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dari pegawai.</t>
+  </si>
+  <si>
+    <t>Ambil alamat dari pegawai.</t>
+  </si>
+  <si>
+    <t>Lihat nama jabatan dari jabatan.</t>
+  </si>
+  <si>
+    <t>Tampilkan gaji pokok dari jabatan.</t>
+  </si>
+  <si>
+    <t>Ambil nama divisi dari divisi.</t>
+  </si>
+  <si>
+    <t>Lihat status dari absensi.</t>
+  </si>
+  <si>
+    <t>Tampilkan tanggal dari absensi.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah gaji dari gaji.</t>
+  </si>
+  <si>
+    <t>Tampilkan bulan dari gaji.</t>
+  </si>
+  <si>
+    <t>Lihat lokasi dari divisi.</t>
+  </si>
+  <si>
+    <t>Ambil harga dari produk.</t>
+  </si>
+  <si>
+    <t>Tampilkan tanggal pesanan dari pesanan.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan status pesanan dari pesanan.</t>
+  </si>
+  <si>
+    <t>Ambil stok dari produk.</t>
+  </si>
+  <si>
+    <t>Tampilkan email dari pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil harga satuan dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama produk dari produk.</t>
+  </si>
+  <si>
+    <t>Ambil telepon dari pelanggan.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dan email dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Ambil nama produk dan harga dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Lihat tanggal pesanan dan total harga dari tabel pesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan jumlah dan sub total dari tabel detailpesanan.</t>
+  </si>
+  <si>
+    <t>Ambil metode pembayaran dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Ambil stok dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Lihat id pesanan dan id pelanggan dari tabel pesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan tanggal bayar dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Ambil harga satuan dari tabel detailpesanan.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dan nim dari mahasiswa yang jurusannya teknik informatika.</t>
+  </si>
+  <si>
+    <t>Ambil email dosen yang bidang keahliannya sistem informasi.</t>
+  </si>
+  <si>
+    <t>Lihat nama mata kuliah dari mata kuliah yang sks-nya lebih dari 3.</t>
+  </si>
+  <si>
+    <t>Tampilkan kapasitas kelas yang tahun akademiknya 2023/2024.</t>
+  </si>
+  <si>
+    <t>Ambil jam mulai dari jadwal yang harinya rabu.</t>
+  </si>
+  <si>
+    <t>Lihat tanggal pendaftaran dari pendaftaran kelas yang id mahasiswa 150.</t>
+  </si>
+  <si>
+    <t>Tampilkan nilai angka dari nilai yang nilai hurufnya sama dengan b.</t>
+  </si>
+  <si>
+    <t>Ambil alamat mahasiswa yang nimnya 20211001.</t>
+  </si>
+  <si>
+    <t>Lihat nip dosen yang namanya mengandung kata “wijaya”.</t>
+  </si>
+  <si>
+    <t>Tampilkan semester mata kuliah yang kode mata kuliahnya seperti ‘MK-01%’.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama akun dari akun dimana tipe akun adalah aset.</t>
+  </si>
+  <si>
+    <t>Ambil tanggal dari jurnal dengan id pengguna sama dengan 3.</t>
+  </si>
+  <si>
+    <t>Perlihatkan debit dari detail jurnal dimana id jurnal sama dengan 10.</t>
+  </si>
+  <si>
+    <t>Ambil nama dari pengguna dengan peran sama dengan admin.</t>
+  </si>
+  <si>
+    <t>Tampilkan saldo debit dari buku besar dimana tanggal sama dengan 2025-05-01.</t>
+  </si>
+  <si>
+    <t>Ambil kode akun dari akun dengan id akun sama dengan 5.</t>
+  </si>
+  <si>
+    <t>Lihat deskripsi dari jurnal dimana tanggal lebih besar dari 2025-04-01.</t>
+  </si>
+  <si>
+    <t>Tampilkan kredit dari detail jurnal dimana debit lebih besar dari 100000.</t>
+  </si>
+  <si>
+    <t>Perlihatkan username dari pengguna dengan nama sama dengan joko.</t>
+  </si>
+  <si>
+    <t>Ambil saldo kredit dari buku besar dimana id akun sama dengan 7.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama produk dari produk dimana jumlah stok lebih dari 100.</t>
+  </si>
+  <si>
+    <t>Ambil nama pelanggan dari pelanggan dimana pelanggan id sama dengan 5.</t>
+  </si>
+  <si>
+    <t>Lihat harga dari produk dimana kategori id adalah 3.</t>
+  </si>
+  <si>
+    <t>Tampilkan tanggal pesanan dari pesananpembelian dimana pemasok id sama dengan 2.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah dari detailpesananpembelian dimana produk id adalah 10.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama pemasok dari pemasok dimana kontak mengandung '0812'.</t>
+  </si>
+  <si>
+    <t>Lihat harga satuan dari detailpesananpenjualan dimana pesanan penjualan id sama dengan 7.</t>
+  </si>
+  <si>
+    <t>Ambil nama kategori dari kategori dimana kategori id adalah 1.</t>
+  </si>
+  <si>
+    <t>Tampilkan deskripsi dari produk dimana produk id sama dengan 15.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah dari detailpesananpenjualan dimana produk id adalah 4.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dan alamat dari pegawai yang jabatan id nya 2.</t>
+  </si>
+  <si>
+    <t>Ambil tanggal dan status dari absensi dimana pegawai id 5.</t>
+  </si>
+  <si>
+    <t>Lihat nama jabatan dari jabatan yang gaji pokok lebih besar dari 5000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama divisi dan lokasi dari divisi yang lokasi nya jakarta.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah gaji dari gaji untuk pegawai id 3 dan bulan 4.</t>
+  </si>
+  <si>
+    <t>Lihat email dari pegawai yang jenis kelamin perempuan.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dan no telepon dari pegawai yang tanggal masuk setelah 2022-01-01.</t>
+  </si>
+  <si>
+    <t>Ambil status dari absensi pada tanggal 2024-05-01.</t>
+  </si>
+  <si>
+    <t>Lihat nama jabatan dari jabatan dengan nama jabatan manager.</t>
+  </si>
+  <si>
+    <t>Tampilkan bulan dan tahun dari gaji yang jumlah gaji lebih dari 10000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama pelanggan dari pelanggan dimana id pelanggan sama dengan 1.</t>
+  </si>
+  <si>
+    <t>Ambil harga dari produk dimana stok lebih dari 10.</t>
+  </si>
+  <si>
+    <t>Tampilkan status pesanan dari pesanan dimana id pesanan sama dengan 5.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah dari detail pesanan dimana id pesanan sama dengan 3.</t>
+  </si>
+  <si>
+    <t>Tampilkan email dari pelanggan dimana nama pelanggan sama dengan 'budi'.</t>
+  </si>
+  <si>
+    <t>Ambil nama produk dari produk dimana harga kurang dari 2000000.</t>
+  </si>
+  <si>
+    <t>Tampilkan telepon dari pelanggan dimana id pelanggan sama dengan 2.</t>
+  </si>
+  <si>
+    <t>Ambil harga satuan dari detail pesanan dimana id produk sama dengan 4.</t>
+  </si>
+  <si>
+    <t>Tampilkan tanggal pesanan dari pesanan dimana status pesanan sama dengan 'proses'.</t>
+  </si>
+  <si>
+    <t>Ambil stok dari produk dimana nama produk sama dengan 'hp samsung'.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dan email dari tabel pelanggan dimana id pelanggan sama dengan 10.</t>
+  </si>
+  <si>
+    <t>Ambil nama produk dan harga dari tabel produk dimana stok lebih besar dari 5.</t>
+  </si>
+  <si>
+    <t>Lihat tanggal pesanan dan total harga dari tabel pesanan dimana id pelanggan sama dengan 3.</t>
+  </si>
+  <si>
+    <t>Tampilkan jumlah dan sub total dari tabel detailpesanan dimana id pesanan sama dengan 7.</t>
+  </si>
+  <si>
+    <t>Ambil metode pembayaran dari tabel pembayaran dimana jumlah bayar lebih dari 100000.</t>
+  </si>
+  <si>
+    <t>Tampilkan nama dari tabel pelanggan dimana alamat mengandung 'bandung'.</t>
+  </si>
+  <si>
+    <t>Ambil stok dari tabel produk dimana harga kurang dari 50000.</t>
+  </si>
+  <si>
+    <t>Lihat id pesanan dan id pelanggan dari tabel pesanan dimana total harga lebih dari 200000.</t>
+  </si>
+  <si>
+    <t>Tampilkan tanggal bayar dari tabel pembayaran dimana metode pembayaran adalah 'kartu kredit'.</t>
+  </si>
+  <si>
+    <t>Ambil harga satuan dari tabel detailpesanan dimana jumlah sama dengan 2.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id mahasiswa dari table mahasiswa.</t>
+  </si>
+  <si>
+    <t>Hitung total kapasitas dari table kelas.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata nilai angka dari table nilai.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimal sks dari table mata kuliah.</t>
+  </si>
+  <si>
+    <t>Cari nilai minimal sks dari table mata kuliah.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id dosen dari table dosen.</t>
+  </si>
+  <si>
+    <t>Hitung total id pendaftaran dari table pendaftaran kelas.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata kapasitas dari table kelas.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimal nilai angka dari table nilai.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id jadwal dari table jadwal.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id akun dari akun.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata debit dari detail jurnal.</t>
+  </si>
+  <si>
+    <t>Tampilkan nilai maksimum saldo debit dari buku besar.</t>
+  </si>
+  <si>
+    <t>Hitung total kredit dari detail jurnal.</t>
+  </si>
+  <si>
+    <t>Cari nilai minimum tanggal dari jurnal.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pengguna dengan menghitung id pengguna.</t>
+  </si>
+  <si>
+    <t>Tampilkan rata-rata saldo kredit dari buku besar.</t>
+  </si>
+  <si>
+    <t>Cari total debit dari detail jurnal.</t>
+  </si>
+  <si>
+    <t>Hitung maksimum kode akun dari akun.</t>
+  </si>
+  <si>
+    <t>Tampilkan nilai minimum saldo debit dari buku besar.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pelanggan dari tabel pelanggan.</t>
+  </si>
+  <si>
+    <t>Jumlahkan total biaya dari tabel reservasi.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah kamar dari tabel kamar.</t>
+  </si>
+  <si>
+    <t>Ambil nilai rata-rata harga per malam dari tabel kamar.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum jumlah pembayaran dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Cari nilai minimum total biaya dari tabel reservasi.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pembayaran dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Jumlahkan jumlah pembayaran dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum total biaya dari tabel reservasi.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah semua produk dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Hitung total harga dari produk.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata harga satuan dari detailpesananpenjualan.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah seluruh pesanan dari pesananpembelian.</t>
+  </si>
+  <si>
+    <t>Cari total jumlah dari detailpesananpembelian.</t>
+  </si>
+  <si>
+    <t>Cari harga tertinggi dari produk.</t>
+  </si>
+  <si>
+    <t>Cari jumlah stok terendah dari produk.</t>
+  </si>
+  <si>
+    <t>Hitung total jumlah produk dari detailpesananpenjualan.</t>
+  </si>
+  <si>
+    <t>Ambil rata-rata jumlah dari detailpesananpembelian.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pegawai dari tabel pegawai.</t>
+  </si>
+  <si>
+    <t>Total seluruh gaji dari tabel gaji.</t>
+  </si>
+  <si>
+    <t>Rata-rata gaji pokok dari tabel jabatan.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum jumlah gaji dari tabel gaji.</t>
+  </si>
+  <si>
+    <t>Cari nilai minimum jumlah gaji dari tabel gaji.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah absensi dari tabel absensi.</t>
+  </si>
+  <si>
+    <t>Rata-rata gaji pokok dari jabatan.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah nama jabatan dari tabel jabatan.</t>
+  </si>
+  <si>
+    <t>Total jumlah gaji dari gaji.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum gaji pokok dari tabel jabatan.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id pelanggan dari pelanggan.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata harga dari produk.</t>
+  </si>
+  <si>
+    <t>Hitung total jumlah dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum harga satuan dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Cari nilai minimum stok dari produk.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pesanan dari tabel pesanan.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata harga satuan dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Hitung total stok dari produk.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum jumlah dari detail pesanan.</t>
+  </si>
+  <si>
+    <t>Cari nilai minimum harga dari produk.</t>
+  </si>
+  <si>
+    <t>Cari total stok dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Hitung total harga dari tabel pesanan.</t>
+  </si>
+  <si>
+    <t>Cari jumlah seluruh sub total dari tabel detailpesanan.</t>
+  </si>
+  <si>
+    <t>Ambil rata-rata harga dari tabel produk.</t>
+  </si>
+  <si>
+    <t>Cari total jumlah dari tabel detailpesanan.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata total harga dari tabel pesanan.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah harga satuan dari tabel detailpesanan.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata jumlah bayar dari tabel pembayaran.</t>
+  </si>
+  <si>
+    <t>Cari jumlah mahasiswa di setiap jurusan yang jumlahnya lebih dari 100.</t>
+  </si>
+  <si>
+    <t>Hitung total kelas per mata kuliah yang lebih dari 3 kelas.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata kapasitas per kelas yang lebih besar dari 40.</t>
+  </si>
+  <si>
+    <t>Cari jumlah dosen berdasarkan bidang keahlian yang jumlahnya lebih dari 2.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pendaftaran per id kelas yang lebih dari 10.</t>
+  </si>
+  <si>
+    <t>Cari jumlah jadwal per hari yang lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata nilai angka per id kelas yang lebih besar dari 70.</t>
+  </si>
+  <si>
+    <t>Cari jumlah mahasiswa per alamat yang jumlahnya lebih dari 20.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah mata kuliah berdasarkan semester yang lebih dari 4.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata sks per semester yang lebih dari 2.</t>
+  </si>
+  <si>
+    <t>Hitung total debit dari detail jurnal group berdasarkan id akun dengan syarat total debit lebih dari 100000.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata saldo kredit dari buku besar group berdasarkan id akun dengan saldo kredit rata-rata di atas 500000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id jurnal dari detail jurnal group berdasarkan id akun dengan jumlah lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Tampilkan maksimum saldo debit dari buku besar group berdasarkan tanggal dengan syarat maksimum saldo debit di atas 1000000.</t>
+  </si>
+  <si>
+    <t>Cari total kredit dari detail jurnal group berdasarkan id jurnal dengan syarat total kredit lebih dari 250000.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata debit dari detail jurnal group berdasarkan id akun dengan debit rata-rata lebih besar dari 10000.</t>
+  </si>
+  <si>
+    <t>Tampilkan total saldo kredit dari buku besar group berdasarkan tanggal dengan syarat total saldo kredit di atas 300000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pengguna dari pengguna group berdasarkan peran dengan jumlah lebih dari 2.</t>
+  </si>
+  <si>
+    <t>Tampilkan maksimum debit dari detail jurnal group berdasarkan id jurnal dengan syarat maksimum debit lebih dari 200000.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata saldo debit dari buku besar group berdasarkan id akun dengan saldo debit rata-rata lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah reservasi dari tabel reservasi berdasarkan tanggal checkin yang memiliki total biaya lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Jumlahkan jumlah pembayaran dari tabel pembayaran berdasarkan metode pembayaran yang totalnya lebih dari 500000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah kamar dari tabel kamar berdasarkan id jenis kamar yang memiliki lebih dari 5 kamar.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah staf dari tabel staf berdasarkan posisi yang jumlahnya lebih dari 2 orang.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pelanggan dari tabel pelanggan berdasarkan email yang digunakan lebih dari satu kali.</t>
+  </si>
+  <si>
+    <t>Jumlahkan total biaya dari tabel reservasi berdasarkan tanggal reservasi yang melebihi 2000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pembayaran dari tabel pembayaran berdasarkan tanggal pembayaran yang lebih dari 3 transaksi.</t>
+  </si>
+  <si>
+    <t>Jumlahkan harga per malam dari tabel kamar berdasarkan status yang totalnya lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah reservasi dari tabel reservasi berdasarkan id kamar yang memiliki lebih dari 2 reservasi.</t>
+  </si>
+  <si>
+    <t>Jumlahkan jumlah pembayaran dari tabel pembayaran berdasarkan id reservasi yang totalnya lebih dari 1500000.</t>
+  </si>
+  <si>
+    <t>Hitung total jumlah dari detailpesananpenjualan dikelompokkan berdasarkan produk id yang jumlahnya lebih dari 50.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata harga dari produk dikelompokkan berdasarkan kategori id yang rata-ratanya di atas 1000000.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah pesanan dari pesananpenjualan dikelompokkan berdasarkan pelanggan id yang jumlahnya lebih dari 3.</t>
+  </si>
+  <si>
+    <t>Hitung total jumlah dari detailpesananpembelian dikelompokkan berdasarkan produk id dengan total lebih dari 20.</t>
+  </si>
+  <si>
+    <t>Cari total harga satuan dari detailpesananpenjualan dikelompokkan berdasarkan pesanan penjualan id yang totalnya lebih dari 500000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah stok dari produk dikelompokkan berdasarkan kategori id dengan stok lebih dari 100.</t>
+  </si>
+  <si>
+    <t>Ambil rata-rata harga dari produk dikelompokkan berdasarkan kategori id yang rata-ratanya kurang dari 500000.</t>
+  </si>
+  <si>
+    <t>Hitung total jumlah dari detailpesananpembelian dikelompokkan berdasarkan pesanan pembelian id yang jumlahnya lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Cari jumlah pesanan dari pesananpembelian dikelompokkan berdasarkan pemasok id yang jumlahnya di atas 2.</t>
+  </si>
+  <si>
+    <t>Ambil total harga satuan dari detailpesananpembelian dikelompokkan berdasarkan produk id dengan total lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pegawai dari tabel pegawai berdasarkan divisi id yang memiliki lebih dari 5 pegawai.</t>
+  </si>
+  <si>
+    <t>Total jumlah gaji dari gaji berdasarkan pegawai id yang totalnya lebih dari 10000000.</t>
+  </si>
+  <si>
+    <t>Rata-rata gaji pokok dari jabatan berdasarkan nama jabatan yang rata-ratanya lebih dari 5000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah absensi dari tabel absensi berdasarkan status yang jumlahnya lebih dari 10.</t>
+  </si>
+  <si>
+    <t>Total jumlah gaji dari tabel gaji berdasarkan bulan yang totalnya lebih dari 15000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pegawai dari tabel pegawai berdasarkan jabatan id yang memiliki lebih dari 3 orang.</t>
+  </si>
+  <si>
+    <t>Rata-rata jumlah gaji dari tabel gaji berdasarkan tahun yang rata-ratanya di atas 7000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah absensi dari tabel absensi berdasarkan pegawai id yang memiliki lebih dari 20 absensi.</t>
+  </si>
+  <si>
+    <t>Total gaji pokok dari tabel jabatan berdasarkan nama jabatan yang totalnya lebih dari 8000000.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pegawai dari tabel pegawai berdasarkan jenis kelamin yang jumlahnya lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id pesanan dari detail pesanan kelompok berdasarkan id pesanan dengan jumlah lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Cari total harga satuan dari detail pesanan kelompok berdasarkan id produk dengan total harga satuan lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata harga dari produk kelompok berdasarkan nama produk dengan rata-rata harga kurang dari 5000000.</t>
+  </si>
+  <si>
+    <t>Cari jumlah id pelanggan dari pelanggan kelompok berdasarkan alamat dengan jumlah id pelanggan lebih dari 10.</t>
+  </si>
+  <si>
+    <t>Hitung total jumlah dari detail pesanan kelompok berdasarkan id produk dengan total jumlah lebih dari 20.</t>
+  </si>
+  <si>
+    <t>Cari nilai maksimum stok dari produk kelompok berdasarkan nama produk dengan stok lebih dari 50.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah id pesanan dari detail pesanan kelompok berdasarkan id produk dengan jumlah id pesanan lebih dari 3.</t>
+  </si>
+  <si>
+    <t>Cari total harga satuan dari detail pesanan kelompok berdasarkan id pesanan dengan total harga satuan lebih dari 500000.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata harga dari produk kelompok berdasarkan nama produk dengan rata-rata harga lebih dari 2000000.</t>
+  </si>
+  <si>
+    <t>Cari jumlah id pelanggan dari pelanggan kelompok berdasarkan email dengan jumlah id pelanggan lebih dari 1.</t>
+  </si>
+  <si>
+    <t>Hitung jumlah pesanan dari tabel pesanan group by id pelanggan dimana total harga lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Cari total jumlah dari detailpesanan group by id produk dimana sub total lebih dari 500000.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata harga dari produk group by nama produk dimana harga lebih dari 100000.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah pembayaran dari pembayaran group by metode pembayaran dimana jumlah bayar lebih dari 200000.</t>
+  </si>
+  <si>
+    <t>Hitung total stok dari produk group by nama produk dimana stok kurang dari 10.</t>
+  </si>
+  <si>
+    <t>Cari jumlah pesanan dari pesanan group by tanggal pesanan dimana total harga kurang dari 500000.</t>
+  </si>
+  <si>
+    <t>Hitung rata-rata jumlah dari detailpesanan group by id pesanan dimana jumlah lebih dari 5.</t>
+  </si>
+  <si>
+    <t>Ambil jumlah pembayaran dari pembayaran group by tanggal bayar dimana jumlah bayar lebih dari 1000000.</t>
+  </si>
+  <si>
+    <t>Hitung total harga dari pesanan group by id pelanggan dimana total harga lebih dari 2000000.</t>
+  </si>
+  <si>
+    <t>Cari rata-rata harga dari produk group by id produk dimana harga kurang dari 75000.</t>
   </si>
 </sst>
 </file>
@@ -1318,12 +1321,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1338,13 +1347,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -33617,11 +33627,11 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" customWidth="1"/>
-    <col min="3" max="3" width="57.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="109.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" customWidth="1"/>
     <col min="7" max="25" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -33664,18 +33674,21 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:25" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>415</v>
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33685,11 +33698,11 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
+      <c r="C3" t="s">
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33699,11 +33712,11 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
+      <c r="C4" t="s">
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33713,11 +33726,11 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
+      <c r="C5" t="s">
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33727,11 +33740,11 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>11</v>
+      <c r="C6" t="s">
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33741,11 +33754,11 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33755,11 +33768,11 @@
       <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
+      <c r="C8" t="s">
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33769,11 +33782,11 @@
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>14</v>
+      <c r="C9" t="s">
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33783,11 +33796,11 @@
       <c r="B10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>15</v>
+      <c r="C10" t="s">
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33797,11 +33810,11 @@
       <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
+      <c r="C11" t="s">
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33811,11 +33824,11 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
+      <c r="C12" t="s">
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33825,11 +33838,11 @@
       <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
+      <c r="C13" t="s">
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33839,11 +33852,11 @@
       <c r="B14" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>19</v>
+      <c r="C14" t="s">
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33853,11 +33866,11 @@
       <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>20</v>
+      <c r="C15" t="s">
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33867,11 +33880,11 @@
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
+      <c r="C16" t="s">
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33881,11 +33894,11 @@
       <c r="B17" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>22</v>
+      <c r="C17" t="s">
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33895,11 +33908,11 @@
       <c r="B18" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>23</v>
+      <c r="C18" t="s">
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33909,11 +33922,11 @@
       <c r="B19" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>24</v>
+      <c r="C19" t="s">
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33923,11 +33936,11 @@
       <c r="B20" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>25</v>
+      <c r="C20" t="s">
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33937,11 +33950,11 @@
       <c r="B21" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>26</v>
+      <c r="C21" t="s">
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33951,11 +33964,11 @@
       <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>27</v>
+      <c r="C22" t="s">
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33965,11 +33978,11 @@
       <c r="B23" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>28</v>
+      <c r="C23" t="s">
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33979,11 +33992,11 @@
       <c r="B24" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>29</v>
+      <c r="C24" t="s">
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -33993,11 +34006,11 @@
       <c r="B25" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>30</v>
+      <c r="C25" t="s">
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34007,11 +34020,11 @@
       <c r="B26" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>31</v>
+      <c r="C26" t="s">
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34021,11 +34034,11 @@
       <c r="B27" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>32</v>
+      <c r="C27" t="s">
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34035,11 +34048,11 @@
       <c r="B28" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>33</v>
+      <c r="C28" t="s">
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34049,11 +34062,11 @@
       <c r="B29" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>34</v>
+      <c r="C29" t="s">
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34063,11 +34076,11 @@
       <c r="B30" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>35</v>
+      <c r="C30" t="s">
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34077,11 +34090,11 @@
       <c r="B31" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>36</v>
+      <c r="C31" t="s">
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34091,11 +34104,11 @@
       <c r="B32" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>37</v>
+      <c r="C32" t="s">
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34105,11 +34118,11 @@
       <c r="B33" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>38</v>
+      <c r="C33" t="s">
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34119,11 +34132,11 @@
       <c r="B34" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>39</v>
+      <c r="C34" t="s">
+        <v>52</v>
       </c>
       <c r="D34" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34133,11 +34146,11 @@
       <c r="B35" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>40</v>
+      <c r="C35" t="s">
+        <v>53</v>
       </c>
       <c r="D35" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34147,11 +34160,11 @@
       <c r="B36" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>41</v>
+      <c r="C36" t="s">
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34161,11 +34174,11 @@
       <c r="B37" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>42</v>
+      <c r="C37" t="s">
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34175,11 +34188,11 @@
       <c r="B38" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>43</v>
+      <c r="C38" t="s">
+        <v>56</v>
       </c>
       <c r="D38" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34189,11 +34202,11 @@
       <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>44</v>
+      <c r="C39" t="s">
+        <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34203,11 +34216,11 @@
       <c r="B40" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>45</v>
+      <c r="C40" t="s">
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34217,11 +34230,11 @@
       <c r="B41" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>46</v>
+      <c r="C41" t="s">
+        <v>59</v>
       </c>
       <c r="D41" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34231,11 +34244,11 @@
       <c r="B42" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>47</v>
+      <c r="C42" t="s">
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34245,11 +34258,11 @@
       <c r="B43" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>48</v>
+      <c r="C43" t="s">
+        <v>61</v>
       </c>
       <c r="D43" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34259,11 +34272,11 @@
       <c r="B44" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>49</v>
+      <c r="C44" t="s">
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34273,11 +34286,11 @@
       <c r="B45" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>50</v>
+      <c r="C45" t="s">
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34287,11 +34300,11 @@
       <c r="B46" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>51</v>
+      <c r="C46" t="s">
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34301,11 +34314,11 @@
       <c r="B47" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>52</v>
+      <c r="C47" t="s">
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34315,11 +34328,11 @@
       <c r="B48" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>53</v>
+      <c r="C48" t="s">
+        <v>66</v>
       </c>
       <c r="D48" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34329,11 +34342,11 @@
       <c r="B49" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>54</v>
+      <c r="C49" t="s">
+        <v>67</v>
       </c>
       <c r="D49" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34343,11 +34356,11 @@
       <c r="B50" t="s">
         <v>6</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>55</v>
+      <c r="C50" t="s">
+        <v>68</v>
       </c>
       <c r="D50" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34357,11 +34370,11 @@
       <c r="B51" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>56</v>
+      <c r="C51" t="s">
+        <v>69</v>
       </c>
       <c r="D51" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34371,11 +34384,11 @@
       <c r="B52" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>57</v>
+      <c r="C52" t="s">
+        <v>70</v>
       </c>
       <c r="D52" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34385,11 +34398,11 @@
       <c r="B53" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>58</v>
+      <c r="C53" t="s">
+        <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34399,11 +34412,11 @@
       <c r="B54" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>59</v>
+      <c r="C54" t="s">
+        <v>72</v>
       </c>
       <c r="D54" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34413,11 +34426,11 @@
       <c r="B55" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>60</v>
+      <c r="C55" t="s">
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34427,11 +34440,11 @@
       <c r="B56" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>61</v>
+      <c r="C56" t="s">
+        <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34441,11 +34454,11 @@
       <c r="B57" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>62</v>
+      <c r="C57" t="s">
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34455,11 +34468,11 @@
       <c r="B58" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>63</v>
+      <c r="C58" t="s">
+        <v>76</v>
       </c>
       <c r="D58" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34469,11 +34482,11 @@
       <c r="B59" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>64</v>
+      <c r="C59" t="s">
+        <v>77</v>
       </c>
       <c r="D59" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34483,11 +34496,11 @@
       <c r="B60" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>65</v>
+      <c r="C60" t="s">
+        <v>78</v>
       </c>
       <c r="D60" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34497,11 +34510,11 @@
       <c r="B61" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>66</v>
+      <c r="C61" t="s">
+        <v>79</v>
       </c>
       <c r="D61" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34511,11 +34524,11 @@
       <c r="B62" t="s">
         <v>6</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>27</v>
+      <c r="C62" t="s">
+        <v>40</v>
       </c>
       <c r="D62" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34525,11 +34538,11 @@
       <c r="B63" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>67</v>
+      <c r="C63" t="s">
+        <v>80</v>
       </c>
       <c r="D63" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34539,11 +34552,11 @@
       <c r="B64" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>68</v>
+      <c r="C64" t="s">
+        <v>81</v>
       </c>
       <c r="D64" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34553,11 +34566,11 @@
       <c r="B65" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>69</v>
+      <c r="C65" t="s">
+        <v>82</v>
       </c>
       <c r="D65" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34567,11 +34580,11 @@
       <c r="B66" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>70</v>
+      <c r="C66" t="s">
+        <v>83</v>
       </c>
       <c r="D66" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34581,11 +34594,11 @@
       <c r="B67" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>71</v>
+      <c r="C67" t="s">
+        <v>84</v>
       </c>
       <c r="D67" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34595,11 +34608,11 @@
       <c r="B68" t="s">
         <v>6</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>72</v>
+      <c r="C68" t="s">
+        <v>85</v>
       </c>
       <c r="D68" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34609,11 +34622,11 @@
       <c r="B69" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>73</v>
+      <c r="C69" t="s">
+        <v>86</v>
       </c>
       <c r="D69" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34623,11 +34636,11 @@
       <c r="B70" t="s">
         <v>6</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>74</v>
+      <c r="C70" t="s">
+        <v>87</v>
       </c>
       <c r="D70" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34637,11 +34650,11 @@
       <c r="B71" t="s">
         <v>6</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>75</v>
+      <c r="C71" t="s">
+        <v>88</v>
       </c>
       <c r="D71" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34649,13 +34662,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D72" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34663,13 +34676,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D73" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34677,13 +34690,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>79</v>
+        <v>7</v>
+      </c>
+      <c r="C74" t="s">
+        <v>91</v>
       </c>
       <c r="D74" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34691,13 +34704,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>80</v>
+        <v>7</v>
+      </c>
+      <c r="C75" t="s">
+        <v>92</v>
       </c>
       <c r="D75" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34705,13 +34718,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>81</v>
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>93</v>
       </c>
       <c r="D76" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34719,13 +34732,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>82</v>
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>94</v>
       </c>
       <c r="D77" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34733,13 +34746,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>83</v>
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>95</v>
       </c>
       <c r="D78" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34747,13 +34760,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>84</v>
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>96</v>
       </c>
       <c r="D79" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34761,13 +34774,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="C80" t="s">
+        <v>97</v>
       </c>
       <c r="D80" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34775,13 +34788,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>86</v>
+        <v>7</v>
+      </c>
+      <c r="C81" t="s">
+        <v>98</v>
       </c>
       <c r="D81" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34789,13 +34802,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D82" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34803,13 +34816,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D83" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34817,13 +34830,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>89</v>
+        <v>7</v>
+      </c>
+      <c r="C84" t="s">
+        <v>101</v>
       </c>
       <c r="D84" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34831,13 +34844,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>76</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>90</v>
+        <v>7</v>
+      </c>
+      <c r="C85" t="s">
+        <v>102</v>
       </c>
       <c r="D85" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34845,13 +34858,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>91</v>
+        <v>7</v>
+      </c>
+      <c r="C86" t="s">
+        <v>103</v>
       </c>
       <c r="D86" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34859,13 +34872,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34873,13 +34886,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>76</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>93</v>
+        <v>7</v>
+      </c>
+      <c r="C88" t="s">
+        <v>105</v>
       </c>
       <c r="D88" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34887,13 +34900,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>76</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>94</v>
+        <v>7</v>
+      </c>
+      <c r="C89" t="s">
+        <v>106</v>
       </c>
       <c r="D89" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34901,13 +34914,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>95</v>
+        <v>7</v>
+      </c>
+      <c r="C90" t="s">
+        <v>107</v>
       </c>
       <c r="D90" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34915,13 +34928,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>76</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>96</v>
+        <v>7</v>
+      </c>
+      <c r="C91" t="s">
+        <v>108</v>
       </c>
       <c r="D91" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34929,13 +34942,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D92" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34943,13 +34956,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D93" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34957,13 +34970,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>76</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>99</v>
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>111</v>
       </c>
       <c r="D94" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34971,13 +34984,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>100</v>
+        <v>7</v>
+      </c>
+      <c r="C95" t="s">
+        <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34985,13 +34998,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>101</v>
+        <v>7</v>
+      </c>
+      <c r="C96" t="s">
+        <v>113</v>
       </c>
       <c r="D96" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -34999,13 +35012,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>102</v>
+        <v>7</v>
+      </c>
+      <c r="C97" t="s">
+        <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35013,13 +35026,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>76</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
+      </c>
+      <c r="C98" t="s">
+        <v>115</v>
       </c>
       <c r="D98" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35027,13 +35040,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D99" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35041,13 +35054,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>76</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
+      </c>
+      <c r="C100" t="s">
+        <v>117</v>
       </c>
       <c r="D100" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35055,13 +35068,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D101" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35069,13 +35082,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D102" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35083,13 +35096,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D103" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35097,13 +35110,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D104" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35111,13 +35124,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D105" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35125,13 +35138,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D106" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35139,13 +35152,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D107" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35153,13 +35166,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D108" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35167,13 +35180,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D109" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35181,13 +35194,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D110" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35195,13 +35208,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D111" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35209,13 +35222,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D112" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35223,13 +35236,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D113" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35237,13 +35250,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>76</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>119</v>
+        <v>7</v>
+      </c>
+      <c r="C114" t="s">
+        <v>131</v>
       </c>
       <c r="D114" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35251,13 +35264,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D115" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35265,13 +35278,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D116" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35279,13 +35292,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>76</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>122</v>
+        <v>7</v>
+      </c>
+      <c r="C117" t="s">
+        <v>134</v>
       </c>
       <c r="D117" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35293,13 +35306,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D118" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35307,13 +35320,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>76</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>124</v>
+        <v>7</v>
+      </c>
+      <c r="C119" t="s">
+        <v>136</v>
       </c>
       <c r="D119" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35321,13 +35334,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D120" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35335,13 +35348,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D121" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35349,13 +35362,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D122" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35363,13 +35376,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D123" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35377,13 +35390,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>76</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>129</v>
+        <v>7</v>
+      </c>
+      <c r="C124" t="s">
+        <v>141</v>
       </c>
       <c r="D124" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35391,13 +35404,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>130</v>
+        <v>7</v>
+      </c>
+      <c r="C125" t="s">
+        <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35405,13 +35418,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>131</v>
+        <v>7</v>
+      </c>
+      <c r="C126" t="s">
+        <v>143</v>
       </c>
       <c r="D126" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35419,13 +35432,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D127" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35433,13 +35446,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>76</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>133</v>
+        <v>7</v>
+      </c>
+      <c r="C128" t="s">
+        <v>145</v>
       </c>
       <c r="D128" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35447,13 +35460,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>76</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>134</v>
+        <v>7</v>
+      </c>
+      <c r="C129" t="s">
+        <v>146</v>
       </c>
       <c r="D129" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35461,13 +35474,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>76</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>135</v>
+        <v>7</v>
+      </c>
+      <c r="C130" t="s">
+        <v>147</v>
       </c>
       <c r="D130" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35475,13 +35488,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D131" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35489,13 +35502,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D132" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35503,13 +35516,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D133" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35517,13 +35530,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D134" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35531,13 +35544,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D135" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35545,13 +35558,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D136" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35559,13 +35572,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>76</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>142</v>
+        <v>7</v>
+      </c>
+      <c r="C137" t="s">
+        <v>154</v>
       </c>
       <c r="D137" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35573,13 +35586,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>76</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>143</v>
+        <v>7</v>
+      </c>
+      <c r="C138" t="s">
+        <v>155</v>
       </c>
       <c r="D138" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35587,13 +35600,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>76</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>144</v>
+        <v>7</v>
+      </c>
+      <c r="C139" t="s">
+        <v>156</v>
       </c>
       <c r="D139" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35601,13 +35614,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D140" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35615,13 +35628,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>76</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>146</v>
+        <v>7</v>
+      </c>
+      <c r="C141" t="s">
+        <v>158</v>
       </c>
       <c r="D141" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35629,13 +35642,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>148</v>
+        <v>8</v>
+      </c>
+      <c r="C142" t="s">
+        <v>159</v>
       </c>
       <c r="D142" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35643,13 +35656,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>149</v>
+        <v>8</v>
+      </c>
+      <c r="C143" t="s">
+        <v>160</v>
       </c>
       <c r="D143" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35657,13 +35670,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>150</v>
+        <v>8</v>
+      </c>
+      <c r="C144" t="s">
+        <v>161</v>
       </c>
       <c r="D144" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35671,13 +35684,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>151</v>
+        <v>8</v>
+      </c>
+      <c r="C145" t="s">
+        <v>162</v>
       </c>
       <c r="D145" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35685,13 +35698,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>147</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>152</v>
+        <v>8</v>
+      </c>
+      <c r="C146" t="s">
+        <v>163</v>
       </c>
       <c r="D146" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35699,13 +35712,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>153</v>
+        <v>8</v>
+      </c>
+      <c r="C147" t="s">
+        <v>164</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35713,13 +35726,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>154</v>
+        <v>8</v>
+      </c>
+      <c r="C148" t="s">
+        <v>165</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35727,13 +35740,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>155</v>
+        <v>8</v>
+      </c>
+      <c r="C149" t="s">
+        <v>166</v>
       </c>
       <c r="D149" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35741,13 +35754,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>147</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>156</v>
+        <v>8</v>
+      </c>
+      <c r="C150" t="s">
+        <v>167</v>
       </c>
       <c r="D150" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35755,13 +35768,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>157</v>
+        <v>8</v>
+      </c>
+      <c r="C151" t="s">
+        <v>168</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35769,13 +35782,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>158</v>
+        <v>8</v>
+      </c>
+      <c r="C152" t="s">
+        <v>169</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35783,13 +35796,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>159</v>
+        <v>8</v>
+      </c>
+      <c r="C153" t="s">
+        <v>170</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35797,13 +35810,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>147</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>160</v>
+        <v>8</v>
+      </c>
+      <c r="C154" t="s">
+        <v>171</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35811,13 +35824,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>147</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+      <c r="C155" t="s">
+        <v>172</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35825,13 +35838,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>147</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>162</v>
+        <v>8</v>
+      </c>
+      <c r="C156" t="s">
+        <v>173</v>
       </c>
       <c r="D156" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35839,13 +35852,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>163</v>
+        <v>8</v>
+      </c>
+      <c r="C157" t="s">
+        <v>174</v>
       </c>
       <c r="D157" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35853,13 +35866,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>147</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>164</v>
+        <v>8</v>
+      </c>
+      <c r="C158" t="s">
+        <v>175</v>
       </c>
       <c r="D158" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35867,13 +35880,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>147</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>165</v>
+        <v>8</v>
+      </c>
+      <c r="C159" t="s">
+        <v>176</v>
       </c>
       <c r="D159" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35881,13 +35894,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>147</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>166</v>
+        <v>8</v>
+      </c>
+      <c r="C160" t="s">
+        <v>177</v>
       </c>
       <c r="D160" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35895,13 +35908,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D161" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35909,13 +35922,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D162" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35923,13 +35936,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D163" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35937,13 +35950,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D164" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35951,13 +35964,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D165" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35965,13 +35978,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D166" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35979,13 +35992,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D167" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -35993,13 +36006,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D168" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -36007,13 +36020,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -36021,13 +36034,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D170" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36035,13 +36048,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C171" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36049,13 +36062,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D172" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36063,13 +36076,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C173" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36077,13 +36090,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C174" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36091,13 +36104,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C175" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36105,13 +36118,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C176" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D176" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36119,13 +36132,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C177" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36133,13 +36146,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C178" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36147,13 +36160,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C179" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36161,13 +36174,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C180" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36175,13 +36188,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D181" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36189,13 +36202,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D182" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36203,13 +36216,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D183" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36217,13 +36230,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D184" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36231,13 +36244,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="D185" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36245,13 +36258,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D186" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36259,13 +36272,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D187" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36273,13 +36286,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D188" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36287,13 +36300,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D189" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36301,13 +36314,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D190" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36315,13 +36328,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D191" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36329,13 +36342,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D192" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36343,13 +36356,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D193" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36357,13 +36370,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D194" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36371,13 +36384,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D195" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36385,13 +36398,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D196" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36399,13 +36412,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D197" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36413,13 +36426,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D198" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36427,13 +36440,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D199" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36441,13 +36454,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D200" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36455,13 +36468,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D201" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36469,13 +36482,13 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D202" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36483,13 +36496,13 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D203" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36497,13 +36510,13 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="D204" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36511,13 +36524,13 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D205" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36525,13 +36538,13 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D206" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36539,13 +36552,13 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D207" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36553,13 +36566,13 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D208" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36567,13 +36580,13 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D209" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36581,13 +36594,13 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D210" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36595,13 +36608,13 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D211" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36609,13 +36622,13 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C212" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D212" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36623,13 +36636,13 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C213" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D213" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36637,13 +36650,13 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C214" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D214" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36651,13 +36664,13 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C215" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D215" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36665,13 +36678,13 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C216" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D216" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36679,13 +36692,13 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C217" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D217" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36693,13 +36706,13 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C218" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D218" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36707,13 +36720,13 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C219" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D219" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36721,13 +36734,13 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C220" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D220" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36735,13 +36748,13 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C221" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D221" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36749,13 +36762,13 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C222" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D222" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36763,13 +36776,13 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C223" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D223" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36777,13 +36790,13 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C224" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D224" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36791,13 +36804,13 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C225" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D225" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36805,13 +36818,13 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C226" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D226" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36819,13 +36832,13 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C227" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D227" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36833,13 +36846,13 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C228" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D228" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36847,13 +36860,13 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C229" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D229" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36861,13 +36874,13 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C230" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D230" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36875,13 +36888,13 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C231" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D231" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36889,13 +36902,13 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C232" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D232" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36903,13 +36916,13 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C233" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D233" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36917,13 +36930,13 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C234" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D234" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36931,13 +36944,13 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C235" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D235" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36945,13 +36958,13 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C236" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D236" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36959,13 +36972,13 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C237" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D237" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36973,13 +36986,13 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C238" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D238" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -36987,13 +37000,13 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C239" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D239" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37001,13 +37014,13 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C240" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D240" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37015,13 +37028,13 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C241" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D241" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37029,13 +37042,13 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C242" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D242" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37043,13 +37056,13 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C243" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D243" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37057,13 +37070,13 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C244" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D244" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37071,13 +37084,13 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C245" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D245" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37085,13 +37098,13 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C246" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="D246" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37099,13 +37112,13 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C247" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="D247" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37113,13 +37126,13 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C248" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D248" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37127,13 +37140,13 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C249" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D249" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37141,13 +37154,13 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C250" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D250" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37155,13 +37168,13 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C251" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D251" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37169,13 +37182,13 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C252" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D252" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37183,13 +37196,13 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C253" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D253" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37197,13 +37210,13 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C254" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D254" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37211,13 +37224,13 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C255" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37225,13 +37238,13 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C256" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D256" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37239,13 +37252,13 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C257" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D257" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37253,13 +37266,13 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C258" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D258" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37267,13 +37280,13 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C259" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D259" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37281,13 +37294,13 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C260" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D260" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37295,13 +37308,13 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C261" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D261" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37309,13 +37322,13 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C262" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D262" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37323,13 +37336,13 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C263" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D263" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37337,13 +37350,13 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C264" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D264" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37351,13 +37364,13 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C265" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D265" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37365,13 +37378,13 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C266" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D266" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37379,13 +37392,13 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C267" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="D267" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37393,13 +37406,13 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C268" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D268" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37407,13 +37420,13 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C269" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D269" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37421,13 +37434,13 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C270" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D270" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37435,13 +37448,13 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C271" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D271" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37449,13 +37462,13 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C272" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D272" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37463,13 +37476,13 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C273" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D273" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37477,13 +37490,13 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C274" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D274" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37491,13 +37504,13 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C275" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="D275" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37505,13 +37518,13 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C276" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D276" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37519,13 +37532,13 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C277" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="D277" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37533,13 +37546,13 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C278" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D278" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37547,13 +37560,13 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C279" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="D279" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37561,13 +37574,13 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C280" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D280" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37575,13 +37588,13 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="C281" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D281" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37589,13 +37602,13 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C282" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D282" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37603,13 +37616,13 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C283" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D283" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37617,13 +37630,13 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C284" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D284" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37631,13 +37644,13 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C285" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D285" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37645,13 +37658,13 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C286" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D286" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37659,13 +37672,13 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C287" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D287" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37673,13 +37686,13 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C288" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="D288" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37687,13 +37700,13 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C289" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D289" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37701,13 +37714,13 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C290" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D290" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37715,13 +37728,13 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C291" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D291" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37729,13 +37742,13 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C292" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D292" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37743,13 +37756,13 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C293" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D293" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37757,13 +37770,13 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C294" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D294" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37771,13 +37784,13 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C295" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D295" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37785,13 +37798,13 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C296" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D296" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37799,13 +37812,13 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C297" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D297" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37813,13 +37826,13 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C298" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D298" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37827,13 +37840,13 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C299" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D299" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37841,13 +37854,13 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C300" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D300" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37855,13 +37868,13 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C301" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D301" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37869,13 +37882,13 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C302" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D302" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37883,13 +37896,13 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C303" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D303" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37897,13 +37910,13 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C304" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D304" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37911,13 +37924,13 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C305" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D305" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37925,13 +37938,13 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C306" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D306" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37939,13 +37952,13 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C307" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D307" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37953,13 +37966,13 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C308" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D308" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37967,13 +37980,13 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C309" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D309" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37981,13 +37994,13 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C310" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D310" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -37995,13 +38008,13 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C311" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D311" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38009,13 +38022,13 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C312" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D312" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38023,13 +38036,13 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C313" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D313" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38037,13 +38050,13 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C314" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D314" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38051,13 +38064,13 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C315" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D315" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38065,13 +38078,13 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C316" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D316" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38079,13 +38092,13 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C317" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D317" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38093,13 +38106,13 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C318" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D318" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38107,13 +38120,13 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C319" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D319" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38121,13 +38134,13 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C320" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D320" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38135,13 +38148,13 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C321" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D321" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38149,13 +38162,13 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C322" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D322" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38163,13 +38176,13 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C323" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D323" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38177,13 +38190,13 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C324" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D324" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38191,13 +38204,13 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C325" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D325" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38205,13 +38218,13 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C326" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D326" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38219,13 +38232,13 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C327" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D327" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38233,13 +38246,13 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C328" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D328" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38247,13 +38260,13 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C329" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D329" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38261,13 +38274,13 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C330" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D330" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38275,13 +38288,13 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C331" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="D331" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38289,13 +38302,13 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C332" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D332" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38303,13 +38316,13 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C333" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D333" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38317,13 +38330,13 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C334" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D334" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38331,13 +38344,13 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C335" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D335" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38345,13 +38358,13 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C336" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D336" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38359,13 +38372,13 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C337" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D337" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38373,13 +38386,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C338" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D338" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38387,13 +38400,13 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C339" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D339" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38401,13 +38414,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C340" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D340" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38415,13 +38428,13 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C341" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D341" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38429,13 +38442,13 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C342" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D342" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38443,13 +38456,13 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C343" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D343" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38457,13 +38470,13 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C344" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D344" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38471,13 +38484,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C345" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D345" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38485,13 +38498,13 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C346" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D346" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38499,13 +38512,13 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C347" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D347" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38513,13 +38526,13 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C348" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D348" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38527,13 +38540,13 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C349" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D349" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38541,13 +38554,13 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C350" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D350" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38555,13 +38568,13 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="C351" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D351" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38569,13 +38582,13 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C352" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D352" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38583,13 +38596,13 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C353" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D353" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38597,13 +38610,13 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C354" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D354" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38611,13 +38624,13 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C355" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D355" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38625,13 +38638,13 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C356" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D356" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38639,13 +38652,13 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C357" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D357" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38653,13 +38666,13 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C358" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D358" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38667,13 +38680,13 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C359" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D359" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38681,13 +38694,13 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C360" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D360" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38695,13 +38708,13 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C361" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D361" t="s">
-        <v>415</v>
+        <v>12</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38709,13 +38722,13 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C362" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D362" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38723,13 +38736,13 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C363" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D363" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38737,13 +38750,13 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C364" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D364" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38751,13 +38764,13 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C365" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D365" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38765,13 +38778,13 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C366" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D366" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38779,13 +38792,13 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C367" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D367" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38793,13 +38806,13 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C368" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D368" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38807,13 +38820,13 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C369" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D369" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38821,13 +38834,13 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C370" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D370" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38835,13 +38848,13 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C371" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D371" t="s">
-        <v>416</v>
+        <v>13</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38849,13 +38862,13 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C372" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="D372" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38863,13 +38876,13 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C373" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D373" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38877,13 +38890,13 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C374" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D374" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38891,13 +38904,13 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C375" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D375" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38905,13 +38918,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C376" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D376" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38919,13 +38932,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C377" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D377" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38933,13 +38946,13 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C378" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="D378" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38947,13 +38960,13 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C379" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D379" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38961,13 +38974,13 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C380" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D380" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38975,13 +38988,13 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C381" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D381" t="s">
-        <v>417</v>
+        <v>14</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -38989,13 +39002,13 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C382" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D382" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39003,13 +39016,13 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C383" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D383" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39017,13 +39030,13 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C384" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D384" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39031,13 +39044,13 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C385" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D385" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39045,13 +39058,13 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C386" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D386" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39059,13 +39072,13 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C387" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="D387" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39073,13 +39086,13 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C388" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D388" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39087,13 +39100,13 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C389" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D389" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39101,13 +39114,13 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C390" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D390" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39115,13 +39128,13 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C391" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D391" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39129,13 +39142,13 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C392" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D392" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39143,13 +39156,13 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C393" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D393" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39157,13 +39170,13 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C394" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D394" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39171,13 +39184,13 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C395" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D395" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39185,13 +39198,13 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C396" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="D396" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39199,13 +39212,13 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C397" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D397" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39213,13 +39226,13 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C398" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D398" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39227,13 +39240,13 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C399" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D399" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39241,13 +39254,13 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C400" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D400" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39255,13 +39268,13 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C401" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D401" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39269,13 +39282,13 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C402" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D402" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39283,13 +39296,13 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C403" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D403" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39297,13 +39310,13 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C404" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D404" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39311,13 +39324,13 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C405" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D405" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39325,13 +39338,13 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C406" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D406" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39339,13 +39352,13 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C407" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D407" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39353,13 +39366,13 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C408" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D408" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39367,13 +39380,13 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C409" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D409" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39381,13 +39394,13 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C410" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D410" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39395,13 +39408,13 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C411" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D411" t="s">
-        <v>420</v>
+        <v>17</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39409,13 +39422,13 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C412" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D412" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39423,13 +39436,13 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C413" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D413" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39437,13 +39450,13 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C414" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D414" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39451,13 +39464,13 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C415" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D415" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39465,13 +39478,13 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C416" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D416" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39479,13 +39492,13 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C417" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D417" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39493,13 +39506,13 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C418" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D418" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39507,13 +39520,13 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C419" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D419" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="420" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39521,13 +39534,13 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C420" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D420" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -39535,13 +39548,13 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>344</v>
+        <v>11</v>
       </c>
       <c r="C421" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="D421" t="s">
-        <v>421</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
